--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacob/Documents/GitHub/AlloyDiscovery/src/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacob/Documents/GitHub/AlloyDiscovery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808CE7FA-5D6E-F341-98B0-B3A392EC65FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C63771B-62A0-2244-8B2E-5ED4E9D1DF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15680" tabRatio="649" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="24">
   <si>
     <t>Name</t>
   </si>
@@ -107,1341 +107,7 @@
     <t>AlCoCrFeNi2.1</t>
   </si>
   <si>
-    <t>AlCoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al0.8CrFeNi2.2</t>
-  </si>
-  <si>
-    <t>Al0.82Cr0.8Fe1.2Ni2.18</t>
-  </si>
-  <si>
-    <t>Al0.83Cr0.6Fe1.4Ni2.17</t>
-  </si>
-  <si>
-    <t>Al0.85Cr0.4Fe1.6Ni2.15</t>
-  </si>
-  <si>
-    <t>Al19.25Co18.86Fe18.36Ni43.53</t>
-  </si>
-  <si>
-    <t>Al0.9CrFeNi</t>
-  </si>
-  <si>
-    <t>AlCrFeNi</t>
-  </si>
-  <si>
-    <t>Al1.1CrFeNi</t>
-  </si>
-  <si>
-    <t>Al1.2CrFeNi</t>
-  </si>
-  <si>
-    <t>Al1.3CrFeNi</t>
-  </si>
-  <si>
-    <t>Co30Cr10Fe10Al18Ni32</t>
-  </si>
-  <si>
-    <t>Co30Cr10Fe10Al18Ni31Mo</t>
-  </si>
-  <si>
-    <t>Co30Cr10Fe10Al18Ni30Mo2</t>
-  </si>
-  <si>
-    <t>Co30Cr10Fe10Al18Ni29Mo3</t>
-  </si>
-  <si>
-    <t>Fe20Co20Ni41Al19</t>
-  </si>
-  <si>
-    <t>Al17Co14.3Cr14.3Fe14.3Ni40.1 (Ae)</t>
-  </si>
-  <si>
-    <t>Al17Co28.6Cr14.3Fe14.3Ni25.8(Be)</t>
-  </si>
-  <si>
-    <t>Al17Co14.3Cr14.3Fe28.6Ni25.8 (Ce)</t>
-  </si>
-  <si>
-    <t>Al0.25CrFeNi1.75</t>
-  </si>
-  <si>
-    <t>Al20.45Co10Cr10Ni59.55 (E10)</t>
-  </si>
-  <si>
-    <t>Al19.3Co15Cr15Ni50.7 (E15)</t>
-  </si>
-  <si>
-    <t>Al17.5Co20Cr20Ni52.5 (E20)</t>
-  </si>
-  <si>
-    <t>Al16.3Co25Cr25Ni33.7 (E25)</t>
-  </si>
-  <si>
-    <t>Al0.25CoCrFe1.25Ni1.25</t>
-  </si>
-  <si>
-    <t>Al14Co24Cr22Fe21Ni19</t>
-  </si>
-  <si>
-    <t>Al16Co23Cr17Fe19Ni25</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi 2.1</t>
-  </si>
-  <si>
-    <t>Al18Co13Cr10Fe14Ni45</t>
-  </si>
-  <si>
-    <t>(Al18Co13Cr10Fe14Ni45)99.5Ti0.5</t>
-  </si>
-  <si>
-    <t>(Al18Co13Cr10Fe14Ni45)99Ti</t>
-  </si>
-  <si>
-    <t>AlCr1.18FeNi2.8</t>
-  </si>
-  <si>
-    <t>AlCrFe1.46Ni2.5</t>
-  </si>
-  <si>
-    <t>Al0.7Cr1.5Fe1.5CoNi</t>
-  </si>
-  <si>
-    <t>Al0.7Cr2Fe1CoNi</t>
-  </si>
-  <si>
-    <t>Al0.7Cr2.5Fe0.5CoNi</t>
-  </si>
-  <si>
-    <t>Al0.7Cr3CoNi</t>
-  </si>
-  <si>
-    <t>Fe30Ni35Cr21.25Al13.75</t>
-  </si>
-  <si>
-    <t>Fe28Ni35Cr18.25Al13.75Co5</t>
-  </si>
-  <si>
-    <t>Fe26Ni35Cr17.25Al13.75Co5Ti3</t>
-  </si>
-  <si>
-    <t>Fe25Ni35Cr16.25Al13.75Co5Ti5</t>
-  </si>
-  <si>
-    <t>Al22Co24Cr20Ni34</t>
-  </si>
-  <si>
-    <t>Al20Co24Cr20Ni36</t>
-  </si>
-  <si>
-    <t>Al28Co24Cr20Ni38</t>
-  </si>
-  <si>
-    <t>Al16Co24Cr20Ni40</t>
-  </si>
-  <si>
-    <t>Al14Co24Cr20Ni42</t>
-  </si>
-  <si>
-    <t>Al18.5Co24Cr20Ni37.5</t>
-  </si>
-  <si>
-    <t>Al17.5Co24Cr20Ni38.5</t>
-  </si>
-  <si>
-    <t>Cr0.25FeNi2.75Al</t>
-  </si>
-  <si>
-    <t>Cr0.5FeNi2.5Al</t>
-  </si>
-  <si>
-    <t>Cr0.75FeNi2.25Al</t>
-  </si>
-  <si>
-    <t>CrFeNi2Al</t>
-  </si>
-  <si>
-    <t>Cr1.25FeNi1.75Al</t>
-  </si>
-  <si>
-    <t>Cr1.5FeNi1.5Al</t>
-  </si>
-  <si>
-    <t>Fe30Cr30Al20Ni20</t>
-  </si>
-  <si>
-    <t>Fe20Cr20Al30Ni30</t>
-  </si>
-  <si>
-    <t>Al7.5Co20.5Fe24Ni24Cr24</t>
-  </si>
-  <si>
-    <t>Al0.3FeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.3Cr0.5FeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.3CrFeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.3Cr1.5FeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.3Cr1.7FeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.3Cr2FeCoNi</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi</t>
-  </si>
-  <si>
-    <t>AlCoCrNi</t>
-  </si>
-  <si>
-    <t>AlCrFe1.5Ni2.6</t>
-  </si>
-  <si>
-    <t>AlCoCrNi2</t>
-  </si>
-  <si>
-    <t>Al0.9CoCrNi2.1</t>
-  </si>
-  <si>
-    <t>Al0.8CoCrNi2.2</t>
-  </si>
-  <si>
-    <t>Al0.7CoCrNi2.3</t>
-  </si>
-  <si>
-    <t>CrFeCoNiAl0.7</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi2.1</t>
-  </si>
-  <si>
-    <t>Al0.7CoCrFeNi2.1</t>
-  </si>
-  <si>
-    <t>Al0.9CoCrFeNi2.1</t>
-  </si>
-  <si>
-    <t>Al1.1CoCrFeNi2.1</t>
-  </si>
-  <si>
-    <t>Al14Co28Cr28Ni30</t>
-  </si>
-  <si>
-    <t>Co23.73Cr23.73Ni23.73Al14.44Fe14.44</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.1-avg</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.0</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.2</t>
-  </si>
-  <si>
-    <t>CrFeNi2.4Al0.6</t>
-  </si>
-  <si>
-    <t>CrFeNi2.3Al0.7</t>
-  </si>
-  <si>
-    <t>CrFeNi2.2Al0.8</t>
-  </si>
-  <si>
-    <t>CrFeNi2.1Al0.9</t>
-  </si>
-  <si>
-    <t>Al0.8CoCr0.6Fe0.7Ni1.1</t>
-  </si>
-  <si>
-    <t>Al0.8CoCr0.6Fe0.7Ni1.5</t>
-  </si>
-  <si>
-    <t>Al0.8CoCr0.6Fe0.7Ni1.8</t>
-  </si>
-  <si>
-    <t>Al0.8CoCr0.6Fe0.7Ni2</t>
-  </si>
-  <si>
-    <t>AlCrFeNi3.1</t>
-  </si>
-  <si>
-    <t>AlCrFe2Ni2.1</t>
-  </si>
-  <si>
-    <t>CrFe2Ni2Mo0.3</t>
-  </si>
-  <si>
-    <t>CrFe2Ni2Mo0.3Nb0.25</t>
-  </si>
-  <si>
-    <t>CrFe2Ni2Mo0.3Nb0.5</t>
-  </si>
-  <si>
-    <t>CrFe2Ni2Mo0.3Nb0.75</t>
-  </si>
-  <si>
-    <t>Al19Co23Fe21Ni37 (Co23)</t>
-  </si>
-  <si>
-    <t>Al18Co27Fe20Ni35 (Co27)</t>
-  </si>
-  <si>
-    <t>Al1CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Al1.1CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Al1.15CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Al1.2CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Al1.25CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Al1.3CoCrFeNi3</t>
-  </si>
-  <si>
-    <t>Ni30Co30Cr10Fe10Al18Mo2</t>
-  </si>
-  <si>
-    <t>Ni40Co20Cr10Fe10Al18Mo2</t>
-  </si>
-  <si>
-    <t>Ni50Co10Cr10Fe10Al18Mo2</t>
-  </si>
-  <si>
-    <t>Ni60Cr10Fe10Al18Mo2</t>
-  </si>
-  <si>
-    <t>NiFeCoCrAl  (N20)</t>
-  </si>
-  <si>
-    <t>Ni1.71FeCoCrAl  (N30)</t>
-  </si>
-  <si>
-    <t>Ni2.67FeCoCrAl  (N40)</t>
-  </si>
-  <si>
-    <t>Ni4FeCoCrAl  (N50)</t>
-  </si>
-  <si>
-    <t>Ni6FeCoCrAl  (N60)</t>
-  </si>
-  <si>
-    <t>Ni9.33FeCoCrAl  (N70)</t>
-  </si>
-  <si>
-    <t>Ni16FeCoCrAl  (N80)</t>
-  </si>
-  <si>
-    <t>AlCo0.4CrFeNi2.7</t>
-  </si>
-  <si>
-    <t>Al0.9CoFeNi2</t>
-  </si>
-  <si>
-    <t>Al0.3CoFeNi</t>
-  </si>
-  <si>
-    <t>CoCrFeNi</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.4</t>
-  </si>
-  <si>
-    <t>AlCrFe2Ni2</t>
-  </si>
-  <si>
-    <t>Ni34.4Al16.4Fe16.4Co16.4Cr16.4</t>
-  </si>
-  <si>
-    <t>Ni34.4Al16.4Fe32.8Cr16.4</t>
-  </si>
-  <si>
-    <t>Ni21.6Al13.9Fe21.5Co21.5Cr21.5</t>
-  </si>
-  <si>
-    <t>Ni33.7Al16.3Fe40Cr10</t>
-  </si>
-  <si>
-    <t>Ni33.7Al16.3Fe50</t>
-  </si>
-  <si>
-    <t>Ni29.6Al15.4Fe45Co10</t>
-  </si>
-  <si>
-    <t>Ni29.6Al15.4Fe55</t>
-  </si>
-  <si>
-    <t>Ni36Co30Fe11Cr11Al6Ti6</t>
-  </si>
-  <si>
-    <t>Co34Cr20Fe20Ni20Al6(CCFNA6)</t>
-  </si>
-  <si>
-    <t>Co29Cr20Fe20Ni20Al11(CCFNA11)</t>
-  </si>
-  <si>
-    <t>Co27Cr20Fe20Ni20Al13(CCFNA13)</t>
-  </si>
-  <si>
-    <t>Co25Cr20Fe20Ni20Al15(CCFNA15)</t>
-  </si>
-  <si>
-    <t>Ni36Co30Fe11Cr11Al6Ti5Nb1</t>
-  </si>
-  <si>
-    <t>Fe11.5 Co20.6 Ni40.7 Cr12.2 Al7.8 Ti7.2</t>
-  </si>
-  <si>
-    <t>Fe40Ni30Cr20Al5Ti5</t>
-  </si>
-  <si>
-    <t>Al15.85Fe11.15Co32.11Cr10.76Ni30.13</t>
-  </si>
-  <si>
-    <t>Ni49.5–Fe19.8–Co15–Cr12–Al3.7</t>
-  </si>
-  <si>
-    <t>Fe36Ni35Al17Cr10Mo2</t>
-  </si>
-  <si>
-    <t>Ni36Co30Cr11Fe11Al10Nb2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni36Co30Cr11Fe11Al8Nb</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni36Co30Cr11Fe11Al6Nb</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni36Co30Cr11Fe11Al4Nb</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>8</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni36Co30Cr11Fe11Al10Nb</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <t>Co2CrFeNi2Al0.3Ti0.3 (Al5Ti5)</t>
-  </si>
-  <si>
-    <t>Co2CrFeNi2Al0.3Ti0.6 (Al5Ti8)</t>
-  </si>
-  <si>
-    <t>Co2CrFeNi2Al0.9Ti0.4 (Al11Ti5)</t>
-  </si>
-  <si>
-    <t>Co36Cr15Fe18Ni18Al8Ti4Mo1</t>
-  </si>
-  <si>
-    <t>Al0.5CrNi1.5Fe2</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi-Nb</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi-3Nb</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi-5Nb</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi-7Nb</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi-9Nb</t>
-  </si>
-  <si>
-    <t>Fe59Ni18Cr13Al10 </t>
-  </si>
-  <si>
-    <t>Al16Cr20Fe10Co30Ni24 </t>
-  </si>
-  <si>
-    <t>Cr18Fe18Co28Ni28Al4Ti4 </t>
-  </si>
-  <si>
-    <t>Fe35Co35Al10Cr10Ni1</t>
-  </si>
-  <si>
-    <t>Ni27.7Cr24Co23.5Fe15.7Mo1.6Al3Ti4.5</t>
-  </si>
-  <si>
-    <t>Al0.7CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al0.6CoCrFeNi</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.1 </t>
-  </si>
-  <si>
-    <t>Fe20Co20Ni41Al19 </t>
-  </si>
-  <si>
-    <t>Ni-32.88wt%Fe-9.53wt%Al</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al0.5Co1.5CrFeNi1.5</t>
-  </si>
-  <si>
-    <t>Ni32.8Fe21.9Co21.9Cr10.9Al7.5Ti5.0</t>
-  </si>
-  <si>
-    <t>Al0.5FeCoCrNi </t>
-  </si>
-  <si>
-    <t> CrFeCoNiAl0.7</t>
-  </si>
-  <si>
-    <t>Al16Co21Cr2Fe21Ni21(Al0.75CoCrFeNi)</t>
-  </si>
-  <si>
-    <t> Al16Co21Cr19.7Fe21Ni21Mo1.3</t>
-  </si>
-  <si>
-    <t> Al16Co21Cr19Fe21Ni21Mo2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Al16Co21Cr2Fe21Ni21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Al0.75CoCrFeNi)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Al16Co21Cr19.7Fe21Ni21Mo</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>1.3</t>
-    </r>
-  </si>
-  <si>
-    <t> Al16Co21Cr17Fe21Ni21Mo4</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNiTi0.1</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNiTi0.2</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNiTi0.3</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNiTi0.4</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNiTi0.5</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNi (7Al-23.25Co-23.25Cr-23.25Fe-23.25Ni in at.%) </t>
-  </si>
-  <si>
-    <t>Al0.2CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al-Co-Cr-Fe-Ni (middle)</t>
-  </si>
-  <si>
-    <t>Al0.45CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al2(NiCoFeCr)14 (M1111)</t>
-  </si>
-  <si>
-    <t>Al2(NiCoFe2Cr)14 (M1121)</t>
-  </si>
-  <si>
-    <t>Al0.4Ni0.4CrFe</t>
-  </si>
-  <si>
-    <t>Al8.33Cr30.38Fe21.97Co20.47Ni18.85</t>
-  </si>
-  <si>
-    <t>Ni35Co25.5Al16 Fe15.5Cr8 </t>
-  </si>
-  <si>
-    <t>Al0.3CrFe0.6CoNi1.4</t>
-  </si>
-  <si>
-    <t>Al0.3CrFeCo0.6Ni1.4</t>
-  </si>
-  <si>
-    <t>Al0.3Cr0.6FeCoNi1.4</t>
-  </si>
-  <si>
-    <t>Al1.2CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Fe60Cr15Ni15Co10</t>
-  </si>
-  <si>
-    <t>Fe60Cr15Ni15Co7Al3</t>
-  </si>
-  <si>
-    <t>Fe60Cr15Ni15Co5Al5</t>
-  </si>
-  <si>
-    <t>Fe60Cr15Ni15Co3Al7</t>
-  </si>
-  <si>
-    <t>Fe60Cr15Ni16Al9</t>
-  </si>
-  <si>
-    <t>Al12.9Co20.9Cr27.3Fe23.9Ni14.9</t>
-  </si>
-  <si>
-    <t>Al0.75NiFeCrCo</t>
-  </si>
-  <si>
-    <t>Al0.75NiFeCr</t>
-  </si>
-  <si>
-    <t>Al0.75NiFeCrCoTi0.25</t>
-  </si>
-  <si>
-    <t>Al₂₀Co₃₀Cr₁₀Fe₁₀Ni₃₀</t>
-  </si>
-  <si>
-    <t>Al₁₈Co₃₀Cr₁₁Fe₁₁Ni₃₀</t>
-  </si>
-  <si>
-    <t>Al₁₆Co₃₀Cr₁₂Fe₁₂Ni₃₀</t>
-  </si>
-  <si>
-    <t>Fe₃.₇₅Cr₁.₂₅NiAl₀.₆ (Ti0)</t>
-  </si>
-  <si>
-    <t>Fe₃.₇₅Cr₁.₂₅NiAl₀.₄₅Ti₀.₁₅ (Ti0.15)</t>
-  </si>
-  <si>
-    <t>Fe₃.₇₅Cr₁.₂₅NiAl₀.₃₀Ti₀.₃₀ (Ti0.3)</t>
-  </si>
-  <si>
-    <t>Fe₃.₇₅Cr₁.₂₅NiAl₀.₂₀Ti₀.₄₀ (Ti0.4)</t>
-  </si>
-  <si>
-    <t>Al5Cr20Fe35Co35Ni5</t>
-  </si>
-  <si>
-    <t>Al17Co17.66Cr17.67Ni47.67</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CoFeNiCr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Al</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0.5(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Cr0.5Al0.5)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CoFeNiCr</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0.75</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Al0.</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Cr0.75Al0.25)</t>
-    </r>
-  </si>
-  <si>
-    <t>CoFeNiCr (Cr1Al0)</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.1Mo0.1</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.1Mo0.2</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.1Mo0.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al0.3CoCrFeNi </t>
-  </si>
-  <si>
-    <t>Al0.1CoCrFeNi</t>
-  </si>
-  <si>
-    <t>(AlNi)40(FeCr)60</t>
-  </si>
-  <si>
-    <t>(AlNi)50(FeCr)50</t>
-  </si>
-  <si>
-    <t>(AlNi)60(FeCr)40</t>
-  </si>
-  <si>
-    <t>CoCrNiFe0.62Al0.38</t>
-  </si>
-  <si>
-    <t>Al19Co25Fe25Ni31 (sample 1)</t>
-  </si>
-  <si>
-    <t>Al20Co22Fe30Ni28(sample 2)</t>
-  </si>
-  <si>
-    <t>Al21Co22Fe29Ni28 (sample 3)</t>
-  </si>
-  <si>
-    <t>Al19.4Fe18.5Co18.5Ni43.6</t>
-  </si>
-  <si>
-    <t>Al17Cr17Co33Ni33</t>
-  </si>
-  <si>
-    <t>CoCrFe₂Ni(Al0)</t>
-  </si>
-  <si>
-    <t>Al₀.₄CoCrFe₂Ni(Al0.4)</t>
-  </si>
-  <si>
-    <t>Al₀.₆CoCrFe₂Ni(Al0.6)</t>
-  </si>
-  <si>
-    <t>Al₀.₈CoCrFe₂Ni(Al0.8)</t>
-  </si>
-  <si>
-    <t>Al0.8CoCrFeNi</t>
-  </si>
-  <si>
-    <t>Al0.1CoCrFe Ni(V0)</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi2.5 </t>
-  </si>
-  <si>
-    <t>Al0.2CoCrFeNi (Al0.2)</t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi (Al0.5)</t>
-  </si>
-  <si>
-    <t>AlCoCrFeNi (Al1)</t>
-  </si>
-  <si>
-    <t> AlCo2.2CrFeNi</t>
-  </si>
-  <si>
-    <t> AlCo2.8CrFeNi</t>
-  </si>
-  <si>
-    <t>Co30Cr30Fe20Ni20</t>
-  </si>
-  <si>
-    <t>Al1.2CoCrFeNi2.1</t>
-  </si>
-  <si>
-    <t>AlCoFeNi2.1</t>
-  </si>
-  <si>
-    <t>AlCoCr0.25FeNi2.1</t>
-  </si>
-  <si>
-    <t>AlCoCr0.5FeNi2.1</t>
-  </si>
-  <si>
-    <t>AlCoCr0.75FeNi2.1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>AlCoCr</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FeNi2.1</t>
-    </r>
-  </si>
-  <si>
-    <t>CoCrFeNi </t>
-  </si>
-  <si>
-    <t>CoCrFeNiMo0.4</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.1Mo0.3</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.2Mo0.2</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.3Mo0.1</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.4</t>
-  </si>
-  <si>
-    <t>Al0.3CoCrFeNi </t>
-  </si>
-  <si>
-    <t>Al0.5CoCrFeNi </t>
-  </si>
-  <si>
-    <t>CoCrFeNi (Ni3Al)0.25</t>
-  </si>
-  <si>
-    <t>CoCrFeNi (Ni3Al)0.5</t>
-  </si>
-  <si>
-    <t>CoCrFeNi (Ni3Al)0.75</t>
-  </si>
-  <si>
-    <t>CoCrFeNi (Ni3Al)1</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Co20Fe30Cr25Ni25 (Co20Fe30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Co30Fe20Cr25Ni25 (Co30Fe20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Co35Fe15Cr25Ni25 (Co35Fe15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.103</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.155</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.206</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.309</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.412</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.25</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.45</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.5</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb0.75</t>
-  </si>
-  <si>
-    <t>CoCrFeNiNb1.0</t>
-  </si>
-  <si>
-    <t>CoCrFeAlNi1.5 (x = 27.3)</t>
-  </si>
-  <si>
-    <t>CoCrFeAlNi3 (x = 42.90)</t>
-  </si>
-  <si>
-    <t>CoCrFeAlNi4 (x =  50)</t>
-  </si>
-  <si>
-    <t>Co33Cr20Ni30Al17</t>
-  </si>
-  <si>
-    <t>Al16Cr20Fe10Co30Ni24</t>
-  </si>
-  <si>
-    <t>Ni1.6_AC</t>
-  </si>
-  <si>
-    <t>Ni1.65_AC</t>
-  </si>
-  <si>
-    <t>Ni1.7_AC</t>
-  </si>
-  <si>
-    <t>Ni1.75_AC</t>
-  </si>
-  <si>
-    <t>Ni1.8_AC</t>
-  </si>
-  <si>
-    <t>Ni1.9_AC</t>
-  </si>
-  <si>
-    <t>Ni2.0_AC_avg</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.1_AC-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>平均值</t>
-    </r>
-  </si>
-  <si>
-    <t>Ni2.5_AC</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni1.7_800℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni1.7_1K℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni1.8_700℃/0.5h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni1.8_800℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni1.8_1K℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.1_600℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.1_800℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.1_1K℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.5_680℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.5_800℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.5_1K℃/1h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ni2.5_1K℃/1.5h/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>水淬</t>
-    </r>
+    <t>MASK</t>
   </si>
 </sst>
 </file>
@@ -1451,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1483,28 +149,6 @@
       <sz val="10.5"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1593,7 +237,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1668,6 +312,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2150,7 +797,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V578"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="2" customWidth="1"/>
     <col min="2" max="9" width="9.5" style="2" customWidth="1"/>
@@ -2163,7 +810,7 @@
     <col min="23" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="98" customHeight="1">
+    <row r="1" spans="1:22" ht="98" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2231,7 +878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -2299,9 +946,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B3" s="2">
         <v>0.16389999999999999</v>
@@ -2367,9 +1014,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B4" s="2">
         <v>0.16389999999999999</v>
@@ -2435,8 +1082,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="2">
@@ -2503,9 +1150,9 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="2" t="s">
-        <v>22</v>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B6" s="2">
         <v>0.16389999999999999</v>
@@ -2571,9 +1218,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B7" s="2">
         <v>0.16389999999999999</v>
@@ -2639,9 +1286,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B8" s="2">
         <v>0.16389999999999999</v>
@@ -2707,9 +1354,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A9" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B9" s="2">
         <v>0.16389999999999999</v>
@@ -2775,9 +1422,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="2" t="s">
-        <v>22</v>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B10" s="2">
         <v>0.16389999999999999</v>
@@ -2843,9 +1490,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B11" s="2">
         <v>0.16</v>
@@ -2911,9 +1558,9 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B12" s="2">
         <v>0.16400000000000001</v>
@@ -2979,9 +1626,9 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
-      <c r="A13" s="2" t="s">
-        <v>26</v>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B13" s="2">
         <v>0.16600000000000001</v>
@@ -3047,9 +1694,9 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
-      <c r="A14" s="2" t="s">
-        <v>27</v>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B14" s="2">
         <v>0.17</v>
@@ -3115,9 +1762,9 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B15" s="2">
         <v>0.1925</v>
@@ -3183,9 +1830,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
-      <c r="A16" s="2" t="s">
-        <v>29</v>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B16" s="2">
         <v>0.23080000000000001</v>
@@ -3251,9 +1898,9 @@
         <v>37.1</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
-      <c r="A17" s="2" t="s">
-        <v>30</v>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B17" s="2">
         <v>0.25</v>
@@ -3319,9 +1966,9 @@
         <v>34.6</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
-      <c r="A18" s="2" t="s">
-        <v>31</v>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B18" s="2">
         <v>0.26829999999999998</v>
@@ -3387,9 +2034,9 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
-      <c r="A19" s="2" t="s">
-        <v>32</v>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B19" s="2">
         <v>0.28570000000000001</v>
@@ -3455,9 +2102,9 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="2" t="s">
-        <v>33</v>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B20" s="2">
         <v>0.30230000000000001</v>
@@ -3523,9 +2170,9 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
-      <c r="A21" s="2" t="s">
-        <v>34</v>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B21" s="2">
         <v>0.18</v>
@@ -3591,9 +2238,9 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
-      <c r="A22" s="2" t="s">
-        <v>35</v>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B22" s="2">
         <v>0.18</v>
@@ -3659,9 +2306,9 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
-      <c r="A23" s="2" t="s">
-        <v>36</v>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="2">
         <v>0.18</v>
@@ -3727,9 +2374,9 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="2" t="s">
-        <v>37</v>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A24" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="2">
         <v>0.18</v>
@@ -3795,9 +2442,9 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="2" t="s">
-        <v>38</v>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B25" s="2">
         <v>0.19</v>
@@ -3863,9 +2510,9 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="2" t="s">
-        <v>39</v>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B26" s="2">
         <v>0.17</v>
@@ -3931,9 +2578,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="2" t="s">
-        <v>40</v>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A27" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B27" s="2">
         <v>0.17</v>
@@ -3999,9 +2646,9 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="2" t="s">
-        <v>41</v>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A28" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B28" s="2">
         <v>0.17</v>
@@ -4067,9 +2714,9 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
-      <c r="A29" s="2" t="s">
-        <v>42</v>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A29" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B29" s="2">
         <v>6.25E-2</v>
@@ -4135,9 +2782,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="2" t="s">
-        <v>43</v>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A30" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B30" s="2">
         <v>0.20449999999999999</v>
@@ -4203,9 +2850,9 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="2" t="s">
-        <v>44</v>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A31" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B31" s="2">
         <v>0.193</v>
@@ -4271,9 +2918,9 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="2" t="s">
-        <v>45</v>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A32" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B32" s="2">
         <v>0.15909999999999999</v>
@@ -4339,9 +2986,9 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="33" spans="1:22">
-      <c r="A33" s="2" t="s">
-        <v>46</v>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A33" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B33" s="2">
         <v>0.16300000000000001</v>
@@ -4407,9 +3054,9 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="34" spans="1:22">
-      <c r="A34" s="2" t="s">
-        <v>47</v>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A34" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B34" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4475,9 +3122,9 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
-      <c r="A35" s="2" t="s">
-        <v>47</v>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A35" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B35" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4543,9 +3190,9 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
-      <c r="A36" s="2" t="s">
-        <v>47</v>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A36" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B36" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4611,9 +3258,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:22">
-      <c r="A37" s="2" t="s">
-        <v>47</v>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A37" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B37" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4679,9 +3326,9 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="38" spans="1:22">
-      <c r="A38" s="2" t="s">
-        <v>47</v>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A38" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B38" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4747,9 +3394,9 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
-      <c r="A39" s="2" t="s">
-        <v>47</v>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B39" s="2">
         <v>5.2600000000000001E-2</v>
@@ -4815,9 +3462,9 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
-      <c r="A40" s="2" t="s">
-        <v>48</v>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A40" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B40" s="2">
         <v>0.14000000000000001</v>
@@ -4883,9 +3530,9 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="41" spans="1:22">
-      <c r="A41" s="2" t="s">
-        <v>49</v>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A41" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B41" s="2">
         <v>0.16</v>
@@ -4951,9 +3598,9 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="42" spans="1:22">
-      <c r="A42" s="2" t="s">
-        <v>22</v>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A42" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B42" s="2">
         <v>0.16389999999999999</v>
@@ -5019,9 +3666,9 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="43" spans="1:22">
-      <c r="A43" s="2" t="s">
-        <v>22</v>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A43" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B43" s="2">
         <v>0.16389999999999999</v>
@@ -5087,9 +3734,9 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="44" spans="1:22">
-      <c r="A44" s="2" t="s">
-        <v>22</v>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A44" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B44" s="2">
         <v>0.16389999999999999</v>
@@ -5155,9 +3802,9 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
-      <c r="A45" s="2" t="s">
-        <v>22</v>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A45" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B45" s="2">
         <v>0.16389999999999999</v>
@@ -5223,9 +3870,9 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
-      <c r="A46" s="2" t="s">
-        <v>22</v>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A46" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B46" s="2">
         <v>0.16389999999999999</v>
@@ -5291,9 +3938,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
-      <c r="A47" s="2" t="s">
-        <v>22</v>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A47" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B47" s="2">
         <v>0.16389999999999999</v>
@@ -5359,9 +4006,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
-      <c r="A48" s="2" t="s">
-        <v>22</v>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A48" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B48" s="2">
         <v>0.16389999999999999</v>
@@ -5427,8 +4074,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
-      <c r="A49" s="2" t="s">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A49" s="25" t="s">
         <v>23</v>
       </c>
       <c r="B49" s="2">
@@ -5495,8 +4142,8 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
-      <c r="A50" s="2" t="s">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A50" s="25" t="s">
         <v>23</v>
       </c>
       <c r="B50" s="2">
@@ -5563,9 +4210,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:22" ht="16">
-      <c r="A51" s="2" t="s">
-        <v>22</v>
+    <row r="51" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B51" s="2">
         <v>0.16389999999999999</v>
@@ -5631,9 +4278,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
-      <c r="A52" s="2" t="s">
-        <v>50</v>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A52" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B52" s="2">
         <v>0.16389999999999999</v>
@@ -5699,9 +4346,9 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
-      <c r="A53" s="2" t="s">
-        <v>22</v>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A53" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B53" s="2">
         <v>0.16389999999999999</v>
@@ -5767,9 +4414,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
-      <c r="A54" s="2" t="s">
-        <v>22</v>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A54" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B54" s="2">
         <v>0.16389999999999999</v>
@@ -5835,9 +4482,9 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
-      <c r="A55" s="2" t="s">
-        <v>22</v>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A55" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B55" s="2">
         <v>0.16389999999999999</v>
@@ -5903,9 +4550,9 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
-      <c r="A56" s="2" t="s">
-        <v>22</v>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A56" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B56" s="2">
         <v>0.16389999999999999</v>
@@ -5971,9 +4618,9 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
-      <c r="A57" s="2" t="s">
-        <v>22</v>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A57" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B57" s="2">
         <v>0.16389999999999999</v>
@@ -6039,9 +4686,9 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
-      <c r="A58" s="2" t="s">
-        <v>22</v>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A58" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B58" s="2">
         <v>0.16389999999999999</v>
@@ -6107,9 +4754,9 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
-      <c r="A59" s="2" t="s">
-        <v>22</v>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A59" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B59" s="2">
         <v>0.16389999999999999</v>
@@ -6175,9 +4822,9 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
-      <c r="A60" s="2" t="s">
-        <v>22</v>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A60" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B60" s="2">
         <v>0.16389999999999999</v>
@@ -6243,9 +4890,9 @@
         <v>13.63</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
-      <c r="A61" s="2" t="s">
-        <v>22</v>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A61" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B61" s="2">
         <v>0.16389999999999999</v>
@@ -6311,9 +4958,9 @@
         <v>14.81</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
-      <c r="A62" s="2" t="s">
-        <v>22</v>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A62" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B62" s="2">
         <v>0.16389999999999999</v>
@@ -6379,9 +5026,9 @@
         <v>14.09</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
-      <c r="A63" s="2" t="s">
-        <v>22</v>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A63" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B63" s="2">
         <v>0.16389999999999999</v>
@@ -6447,9 +5094,9 @@
         <v>14.43</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
-      <c r="A64" s="2" t="s">
-        <v>22</v>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A64" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B64" s="2">
         <v>0.16389999999999999</v>
@@ -6515,9 +5162,9 @@
         <v>15.46</v>
       </c>
     </row>
-    <row r="65" spans="1:22">
-      <c r="A65" s="2" t="s">
-        <v>22</v>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A65" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B65" s="2">
         <v>0.16389999999999999</v>
@@ -6583,9 +5230,9 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
-      <c r="A66" s="2" t="s">
-        <v>22</v>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A66" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B66" s="2">
         <v>0.16389999999999999</v>
@@ -6651,9 +5298,9 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="67" spans="1:22">
-      <c r="A67" s="2" t="s">
-        <v>22</v>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A67" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B67" s="2">
         <v>0.16389999999999999</v>
@@ -6719,9 +5366,9 @@
         <v>15.41</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
-      <c r="A68" s="2" t="s">
-        <v>22</v>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A68" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B68" s="2">
         <v>0.16389999999999999</v>
@@ -6787,9 +5434,9 @@
         <v>16.18</v>
       </c>
     </row>
-    <row r="69" spans="1:22">
-      <c r="A69" s="2" t="s">
-        <v>22</v>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A69" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B69" s="2">
         <v>0.16389999999999999</v>
@@ -6855,9 +5502,9 @@
         <v>16.78</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
-      <c r="A70" s="2" t="s">
-        <v>22</v>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A70" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B70" s="2">
         <v>0.16389999999999999</v>
@@ -6923,9 +5570,9 @@
         <v>18.79</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
-      <c r="A71" s="2" t="s">
-        <v>22</v>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A71" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B71" s="2">
         <v>0.16389999999999999</v>
@@ -6991,9 +5638,9 @@
         <v>18.940000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
-      <c r="A72" s="2" t="s">
-        <v>22</v>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A72" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B72" s="2">
         <v>0.16389999999999999</v>
@@ -7059,9 +5706,9 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
-      <c r="A73" s="2" t="s">
-        <v>22</v>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A73" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B73" s="2">
         <v>0.16389999999999999</v>
@@ -7127,9 +5774,9 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="74" spans="1:22">
-      <c r="A74" s="2" t="s">
-        <v>22</v>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A74" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B74" s="2">
         <v>0.16389999999999999</v>
@@ -7195,9 +5842,9 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="75" spans="1:22">
-      <c r="A75" s="2" t="s">
-        <v>22</v>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A75" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B75" s="2">
         <v>0.16389999999999999</v>
@@ -7263,9 +5910,9 @@
         <v>18.86</v>
       </c>
     </row>
-    <row r="76" spans="1:22">
-      <c r="A76" s="2" t="s">
-        <v>22</v>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A76" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B76" s="2">
         <v>0.16389999999999999</v>
@@ -7331,9 +5978,9 @@
         <v>19.04</v>
       </c>
     </row>
-    <row r="77" spans="1:22">
-      <c r="A77" s="2" t="s">
-        <v>22</v>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A77" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B77" s="2">
         <v>0.16389999999999999</v>
@@ -7399,9 +6046,9 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="78" spans="1:22">
-      <c r="A78" s="2" t="s">
-        <v>22</v>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A78" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B78" s="2">
         <v>0.16389999999999999</v>
@@ -7467,9 +6114,9 @@
         <v>19.420000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:22">
-      <c r="A79" s="2" t="s">
-        <v>22</v>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A79" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B79" s="2">
         <v>0.16389999999999999</v>
@@ -7535,9 +6182,9 @@
         <v>20.18</v>
       </c>
     </row>
-    <row r="80" spans="1:22">
-      <c r="A80" s="2" t="s">
-        <v>51</v>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A80" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B80" s="2">
         <v>0.18</v>
@@ -7603,9 +6250,9 @@
         <v>10.83</v>
       </c>
     </row>
-    <row r="81" spans="1:22">
-      <c r="A81" s="2" t="s">
-        <v>52</v>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A81" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B81" s="2">
         <v>0.17910000000000001</v>
@@ -7671,9 +6318,9 @@
         <v>9.18</v>
       </c>
     </row>
-    <row r="82" spans="1:22">
-      <c r="A82" s="2" t="s">
-        <v>53</v>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A82" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B82" s="2">
         <v>0.1782</v>
@@ -7739,9 +6386,9 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="83" spans="1:22">
-      <c r="A83" s="2" t="s">
-        <v>54</v>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A83" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B83" s="2">
         <v>0.16719999999999999</v>
@@ -7807,9 +6454,9 @@
         <v>40.1</v>
       </c>
     </row>
-    <row r="84" spans="1:22">
-      <c r="A84" s="2" t="s">
-        <v>55</v>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A84" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B84" s="2">
         <v>0.1678</v>
@@ -7875,9 +6522,9 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="85" spans="1:22">
-      <c r="A85" s="2" t="s">
-        <v>56</v>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A85" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B85" s="2">
         <v>0.12280000000000001</v>
@@ -7943,9 +6590,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" spans="1:22">
-      <c r="A86" s="2" t="s">
-        <v>57</v>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A86" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B86" s="2">
         <v>0.12280000000000001</v>
@@ -8011,9 +6658,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:22">
-      <c r="A87" s="2" t="s">
-        <v>58</v>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A87" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B87" s="2">
         <v>0.12280000000000001</v>
@@ -8079,9 +6726,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:22">
-      <c r="A88" s="2" t="s">
-        <v>59</v>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A88" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B88" s="2">
         <v>0.12280000000000001</v>
@@ -8147,9 +6794,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:22">
-      <c r="A89" s="2" t="s">
-        <v>60</v>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A89" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B89" s="2">
         <v>0.13750000000000001</v>
@@ -8215,9 +6862,9 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="90" spans="1:22">
-      <c r="A90" s="2" t="s">
-        <v>61</v>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A90" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B90" s="2">
         <v>0.13750000000000001</v>
@@ -8283,9 +6930,9 @@
         <v>37.799999999999997</v>
       </c>
     </row>
-    <row r="91" spans="1:22">
-      <c r="A91" s="2" t="s">
-        <v>62</v>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A91" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B91" s="2">
         <v>0.13750000000000001</v>
@@ -8351,9 +6998,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="92" spans="1:22">
-      <c r="A92" s="2" t="s">
-        <v>63</v>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A92" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B92" s="2">
         <v>0.13750000000000001</v>
@@ -8419,9 +7066,9 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="93" spans="1:22">
-      <c r="A93" s="2" t="s">
-        <v>64</v>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A93" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B93" s="2">
         <v>0.22</v>
@@ -8487,9 +7134,9 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:22">
-      <c r="A94" s="2" t="s">
-        <v>65</v>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A94" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B94" s="2">
         <v>0.2</v>
@@ -8555,9 +7202,9 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="95" spans="1:22">
-      <c r="A95" s="2" t="s">
-        <v>66</v>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A95" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B95" s="2">
         <v>0.2545</v>
@@ -8623,9 +7270,9 @@
         <v>8.1</v>
       </c>
     </row>
-    <row r="96" spans="1:22">
-      <c r="A96" s="2" t="s">
-        <v>67</v>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A96" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B96" s="2">
         <v>0.16</v>
@@ -8691,9 +7338,9 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="97" spans="1:22">
-      <c r="A97" s="2" t="s">
-        <v>68</v>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A97" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B97" s="2">
         <v>0.14000000000000001</v>
@@ -8759,9 +7406,9 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="98" spans="1:22">
-      <c r="A98" s="2" t="s">
-        <v>69</v>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A98" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B98" s="2">
         <v>0.185</v>
@@ -8827,9 +7474,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:22">
-      <c r="A99" s="2" t="s">
-        <v>70</v>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A99" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B99" s="2">
         <v>0.17499999999999999</v>
@@ -8895,9 +7542,9 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="100" spans="1:22">
-      <c r="A100" s="2" t="s">
-        <v>71</v>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A100" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B100" s="2">
         <v>0.2</v>
@@ -8963,9 +7610,9 @@
         <v>51.69</v>
       </c>
     </row>
-    <row r="101" spans="1:22">
-      <c r="A101" s="2" t="s">
-        <v>72</v>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A101" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B101" s="2">
         <v>0.2</v>
@@ -9031,9 +7678,9 @@
         <v>43.78</v>
       </c>
     </row>
-    <row r="102" spans="1:22">
-      <c r="A102" s="2" t="s">
-        <v>73</v>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A102" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B102" s="2">
         <v>0.2</v>
@@ -9099,9 +7746,9 @@
         <v>48.31</v>
       </c>
     </row>
-    <row r="103" spans="1:22">
-      <c r="A103" s="2" t="s">
-        <v>74</v>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A103" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B103" s="2">
         <v>0.2</v>
@@ -9167,9 +7814,9 @@
         <v>39.04</v>
       </c>
     </row>
-    <row r="104" spans="1:22">
-      <c r="A104" s="2" t="s">
-        <v>75</v>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A104" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B104" s="2">
         <v>0.2</v>
@@ -9235,9 +7882,9 @@
         <v>41.36</v>
       </c>
     </row>
-    <row r="105" spans="1:22">
-      <c r="A105" s="2" t="s">
-        <v>76</v>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A105" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B105" s="2">
         <v>0.2</v>
@@ -9303,9 +7950,9 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="106" spans="1:22">
-      <c r="A106" s="2" t="s">
-        <v>77</v>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A106" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B106" s="2">
         <v>0.2</v>
@@ -9371,9 +8018,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="1:22">
-      <c r="A107" s="2" t="s">
-        <v>78</v>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A107" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B107" s="2">
         <v>0.3</v>
@@ -9439,9 +8086,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="108" spans="1:22">
-      <c r="A108" s="2" t="s">
-        <v>79</v>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A108" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B108" s="2">
         <v>7.4999999999999997E-2</v>
@@ -9507,9 +8154,9 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="109" spans="1:22">
-      <c r="A109" s="2" t="s">
-        <v>79</v>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A109" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B109" s="2">
         <v>7.4999999999999997E-2</v>
@@ -9575,9 +8222,9 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="110" spans="1:22">
-      <c r="A110" s="2" t="s">
-        <v>79</v>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A110" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B110" s="2">
         <v>7.4999999999999997E-2</v>
@@ -9643,9 +8290,9 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="111" spans="1:22">
-      <c r="A111" s="2" t="s">
-        <v>79</v>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A111" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B111" s="2">
         <v>7.4999999999999997E-2</v>
@@ -9711,9 +8358,9 @@
         <v>35.1</v>
       </c>
     </row>
-    <row r="112" spans="1:22">
-      <c r="A112" s="2" t="s">
-        <v>80</v>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A112" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B112" s="2">
         <v>9.0899999999999995E-2</v>
@@ -9779,9 +8426,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="1:22">
-      <c r="A113" s="2" t="s">
-        <v>81</v>
+    <row r="113" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A113" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B113" s="2">
         <v>7.8899999999999998E-2</v>
@@ -9847,9 +8494,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="114" spans="1:22">
-      <c r="A114" s="2" t="s">
-        <v>82</v>
+    <row r="114" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A114" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B114" s="2">
         <v>6.9800000000000001E-2</v>
@@ -9915,9 +8562,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="115" spans="1:22">
-      <c r="A115" s="2" t="s">
-        <v>83</v>
+    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A115" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B115" s="2">
         <v>6.25E-2</v>
@@ -9983,9 +8630,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="1:22">
-      <c r="A116" s="2" t="s">
-        <v>84</v>
+    <row r="116" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A116" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B116" s="2">
         <v>0.06</v>
@@ -10051,9 +8698,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:22">
-      <c r="A117" s="2" t="s">
-        <v>85</v>
+    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A117" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B117" s="2">
         <v>5.6599999999999998E-2</v>
@@ -10119,9 +8766,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:22">
-      <c r="A118" s="2" t="s">
-        <v>86</v>
+    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A118" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B118" s="2">
         <v>0.1111</v>
@@ -10187,9 +8834,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:22">
-      <c r="A119" s="2" t="s">
-        <v>86</v>
+    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A119" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B119" s="2">
         <v>0.1111</v>
@@ -10255,9 +8902,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:22">
-      <c r="A120" s="2" t="s">
-        <v>86</v>
+    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A120" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B120" s="2">
         <v>0.1111</v>
@@ -10323,9 +8970,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:22">
-      <c r="A121" s="2" t="s">
-        <v>87</v>
+    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A121" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B121" s="2">
         <v>0.25</v>
@@ -10391,9 +9038,9 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="122" spans="1:22" ht="16">
-      <c r="A122" s="2" t="s">
-        <v>88</v>
+    <row r="122" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A122" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B122" s="2">
         <v>0.16389999999999999</v>
@@ -10459,9 +9106,9 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="123" spans="1:22" ht="16">
-      <c r="A123" s="2" t="s">
-        <v>89</v>
+    <row r="123" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A123" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B123" s="2">
         <v>0.2</v>
@@ -10527,9 +9174,9 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="124" spans="1:22" ht="16">
-      <c r="A124" s="2" t="s">
-        <v>90</v>
+    <row r="124" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A124" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B124" s="2">
         <v>0.18</v>
@@ -10595,9 +9242,9 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="125" spans="1:22" ht="16">
-      <c r="A125" s="2" t="s">
-        <v>91</v>
+    <row r="125" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A125" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B125" s="3">
         <v>0.16</v>
@@ -10663,9 +9310,9 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="126" spans="1:22" ht="16">
-      <c r="A126" s="2" t="s">
-        <v>92</v>
+    <row r="126" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A126" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B126" s="3">
         <v>0.14000000000000001</v>
@@ -10731,9 +9378,9 @@
         <v>26.2</v>
       </c>
     </row>
-    <row r="127" spans="1:22" ht="16">
-      <c r="A127" s="2" t="s">
-        <v>90</v>
+    <row r="127" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A127" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B127" s="3">
         <v>0.18</v>
@@ -10799,9 +9446,9 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="128" spans="1:22" ht="16">
-      <c r="A128" s="2" t="s">
-        <v>93</v>
+    <row r="128" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A128" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B128" s="3">
         <v>0.1489</v>
@@ -10867,9 +9514,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:22" ht="18">
-      <c r="A129" s="2" t="s">
-        <v>94</v>
+    <row r="129" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A129" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B129" s="3">
         <v>8.9300000000000004E-2</v>
@@ -10935,9 +9582,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="130" spans="1:22" ht="18">
-      <c r="A130" s="2" t="s">
-        <v>95</v>
+    <row r="130" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A130" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B130" s="2">
         <v>0.1207</v>
@@ -11003,9 +9650,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="131" spans="1:22" ht="18">
-      <c r="A131" s="2" t="s">
-        <v>96</v>
+    <row r="131" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A131" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B131" s="2">
         <v>0.15</v>
@@ -11071,9 +9718,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:22" ht="18">
-      <c r="A132" s="2" t="s">
-        <v>97</v>
+    <row r="132" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A132" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B132" s="2">
         <v>0.1774</v>
@@ -11139,9 +9786,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="133" spans="1:22" ht="16">
-      <c r="A133" s="2" t="s">
-        <v>98</v>
+    <row r="133" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A133" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B133" s="2">
         <v>0.14000000000000001</v>
@@ -11207,9 +9854,9 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="134" spans="1:22" ht="16">
-      <c r="A134" s="2" t="s">
-        <v>99</v>
+    <row r="134" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A134" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B134" s="2">
         <v>0.14430000000000001</v>
@@ -11275,9 +9922,9 @@
         <v>33.799999999999997</v>
       </c>
     </row>
-    <row r="135" spans="1:22" ht="16">
-      <c r="A135" s="2" t="s">
-        <v>22</v>
+    <row r="135" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A135" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B135" s="2">
         <v>0.16389999999999999</v>
@@ -11343,9 +9990,9 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="136" spans="1:22" ht="16">
-      <c r="A136" s="2" t="s">
-        <v>22</v>
+    <row r="136" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A136" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B136" s="2">
         <v>0.16389999999999999</v>
@@ -11411,9 +10058,9 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="137" spans="1:22" ht="16">
-      <c r="A137" s="2" t="s">
-        <v>22</v>
+    <row r="137" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A137" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B137" s="2">
         <v>0.16389999999999999</v>
@@ -11479,9 +10126,9 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="138" spans="1:22">
-      <c r="A138" s="2" t="s">
-        <v>100</v>
+    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A138" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B138" s="2">
         <v>0.16389999999999999</v>
@@ -11547,9 +10194,9 @@
         <v>32.880000000000003</v>
       </c>
     </row>
-    <row r="139" spans="1:22" ht="16">
-      <c r="A139" s="8" t="s">
-        <v>101</v>
+    <row r="139" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A139" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B139" s="2">
         <v>0.16669999999999999</v>
@@ -11615,9 +10262,9 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="140" spans="1:22" ht="16">
-      <c r="A140" s="8" t="s">
-        <v>22</v>
+    <row r="140" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A140" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B140" s="2">
         <v>0.16389999999999999</v>
@@ -11683,9 +10330,9 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="141" spans="1:22" ht="16">
-      <c r="A141" s="8" t="s">
-        <v>102</v>
+    <row r="141" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A141" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B141" s="2">
         <v>0.1613</v>
@@ -11751,9 +10398,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:22" ht="16">
-      <c r="A142" s="8" t="s">
-        <v>101</v>
+    <row r="142" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A142" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B142" s="2">
         <v>0.16669999999999999</v>
@@ -11819,9 +10466,9 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="143" spans="1:22" ht="16">
-      <c r="A143" s="8" t="s">
-        <v>22</v>
+    <row r="143" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A143" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B143" s="2">
         <v>0.16389999999999999</v>
@@ -11887,9 +10534,9 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="144" spans="1:22" ht="16">
-      <c r="A144" s="9" t="s">
-        <v>102</v>
+    <row r="144" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A144" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B144" s="2">
         <v>0.1613</v>
@@ -11955,9 +10602,9 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="145" spans="1:22">
-      <c r="A145" s="2" t="s">
-        <v>103</v>
+    <row r="145" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A145" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B145" s="2">
         <v>0.12</v>
@@ -12023,9 +10670,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="146" spans="1:22">
-      <c r="A146" s="2" t="s">
-        <v>104</v>
+    <row r="146" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A146" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B146" s="2">
         <v>0.14000000000000001</v>
@@ -12091,9 +10738,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="147" spans="1:22">
-      <c r="A147" s="2" t="s">
-        <v>105</v>
+    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A147" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B147" s="2">
         <v>0.16</v>
@@ -12159,9 +10806,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="148" spans="1:22">
-      <c r="A148" s="2" t="s">
-        <v>106</v>
+    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A148" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B148" s="2">
         <v>0.18</v>
@@ -12227,9 +10874,9 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="149" spans="1:22">
-      <c r="A149" s="2" t="s">
-        <v>74</v>
+    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A149" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B149" s="2">
         <v>0.2</v>
@@ -12295,9 +10942,9 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="150" spans="1:22">
-      <c r="A150" s="2" t="s">
-        <v>102</v>
+    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A150" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B150" s="2">
         <v>0.1613</v>
@@ -12363,9 +11010,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
-      <c r="A151" s="2" t="s">
-        <v>102</v>
+    <row r="151" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A151" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B151" s="2">
         <v>0.1613</v>
@@ -12431,9 +11078,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:22">
-      <c r="A152" s="2" t="s">
-        <v>107</v>
+    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A152" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B152" s="2">
         <v>0.1905</v>
@@ -12499,9 +11146,9 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="153" spans="1:22">
-      <c r="A153" s="2" t="s">
-        <v>108</v>
+    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A153" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B153" s="2">
         <v>0.1739</v>
@@ -12567,9 +11214,9 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="154" spans="1:22">
-      <c r="A154" s="2" t="s">
-        <v>109</v>
+    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A154" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B154" s="2">
         <v>0.1633</v>
@@ -12635,9 +11282,9 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:22">
-      <c r="A155" s="2" t="s">
-        <v>110</v>
+    <row r="155" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A155" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B155" s="2">
         <v>0.15690000000000001</v>
@@ -12703,9 +11350,9 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="156" spans="1:22">
-      <c r="A156" s="2" t="s">
-        <v>111</v>
+    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A156" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B156" s="2">
         <v>0.16389999999999999</v>
@@ -12771,9 +11418,9 @@
         <v>21.07</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
-      <c r="A157" s="2" t="s">
-        <v>112</v>
+    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A157" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B157" s="2">
         <v>0.16389999999999999</v>
@@ -12839,9 +11486,9 @@
         <v>23.31</v>
       </c>
     </row>
-    <row r="158" spans="1:22" ht="18">
-      <c r="A158" s="2" t="s">
-        <v>113</v>
+    <row r="158" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A158" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B158" s="2">
         <v>0</v>
@@ -12907,9 +11554,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="1:22" ht="18">
-      <c r="A159" s="2" t="s">
-        <v>114</v>
+    <row r="159" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A159" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B159" s="2">
         <v>0</v>
@@ -12975,9 +11622,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="18">
-      <c r="A160" s="2" t="s">
-        <v>115</v>
+    <row r="160" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A160" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B160" s="2">
         <v>0</v>
@@ -13043,9 +11690,9 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="161" spans="1:22" ht="18">
-      <c r="A161" s="2" t="s">
-        <v>116</v>
+    <row r="161" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A161" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B161" s="2">
         <v>0</v>
@@ -13111,9 +11758,9 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="162" spans="1:22">
-      <c r="A162" s="2" t="s">
-        <v>117</v>
+    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A162" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B162" s="2">
         <v>0.19</v>
@@ -13179,9 +11826,9 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="163" spans="1:22">
-      <c r="A163" s="2" t="s">
-        <v>118</v>
+    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A163" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B163" s="2">
         <v>0.18</v>
@@ -13247,9 +11894,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="164" spans="1:22" ht="15">
-      <c r="A164" s="10" t="s">
-        <v>119</v>
+    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A164" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B164" s="2">
         <v>0.1429</v>
@@ -13315,9 +11962,9 @@
         <v>31.16</v>
       </c>
     </row>
-    <row r="165" spans="1:22" ht="15">
-      <c r="A165" s="3" t="s">
-        <v>120</v>
+    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A165" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B165" s="2">
         <v>0.15490000000000001</v>
@@ -13383,9 +12030,9 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="166" spans="1:22" ht="15">
-      <c r="A166" s="3" t="s">
-        <v>121</v>
+    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A166" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B166" s="2">
         <v>0.1608</v>
@@ -13451,9 +12098,9 @@
         <v>21.7</v>
       </c>
     </row>
-    <row r="167" spans="1:22" ht="15">
-      <c r="A167" s="3" t="s">
-        <v>122</v>
+    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A167" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B167" s="2">
         <v>0.16669999999999999</v>
@@ -13519,9 +12166,9 @@
         <v>15.01</v>
       </c>
     </row>
-    <row r="168" spans="1:22" ht="15">
-      <c r="A168" s="3" t="s">
-        <v>123</v>
+    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A168" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B168" s="2">
         <v>0.1724</v>
@@ -13587,9 +12234,9 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="169" spans="1:22" ht="15">
-      <c r="A169" s="11" t="s">
-        <v>124</v>
+    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A169" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B169" s="2">
         <v>0.17810000000000001</v>
@@ -13655,9 +12302,9 @@
         <v>13.46</v>
       </c>
     </row>
-    <row r="170" spans="1:22">
-      <c r="A170" s="2" t="s">
-        <v>125</v>
+    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A170" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B170" s="2">
         <v>0.18</v>
@@ -13723,9 +12370,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:22">
-      <c r="A171" s="2" t="s">
-        <v>126</v>
+    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A171" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B171" s="2">
         <v>0.18</v>
@@ -13791,9 +12438,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:22">
-      <c r="A172" s="2" t="s">
-        <v>127</v>
+    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A172" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B172" s="2">
         <v>0.18</v>
@@ -13859,9 +12506,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:22">
-      <c r="A173" s="2" t="s">
-        <v>128</v>
+    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A173" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B173" s="2">
         <v>0.18</v>
@@ -13927,9 +12574,9 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="174" spans="1:22" ht="16">
-      <c r="A174" s="3" t="s">
-        <v>129</v>
+    <row r="174" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A174" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B174" s="2">
         <v>0.2</v>
@@ -13995,9 +12642,9 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="175" spans="1:22" ht="16">
-      <c r="A175" s="3" t="s">
-        <v>130</v>
+    <row r="175" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A175" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B175" s="2">
         <v>0.17510000000000001</v>
@@ -14063,9 +12710,9 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="176" spans="1:22" ht="16">
-      <c r="A176" s="3" t="s">
-        <v>131</v>
+    <row r="176" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A176" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B176" s="2">
         <v>0.14990000000000001</v>
@@ -14131,9 +12778,9 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="177" spans="1:22" ht="16">
-      <c r="A177" s="3" t="s">
-        <v>132</v>
+    <row r="177" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A177" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B177" s="2">
         <v>0.125</v>
@@ -14199,9 +12846,9 @@
         <v>56.3</v>
       </c>
     </row>
-    <row r="178" spans="1:22" ht="16">
-      <c r="A178" s="3" t="s">
-        <v>133</v>
+    <row r="178" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A178" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B178" s="2">
         <v>0.1</v>
@@ -14267,9 +12914,9 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="179" spans="1:22" ht="16">
-      <c r="A179" s="3" t="s">
-        <v>134</v>
+    <row r="179" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A179" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B179" s="2">
         <v>7.4999999999999997E-2</v>
@@ -14335,9 +12982,9 @@
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="180" spans="1:22" ht="16">
-      <c r="A180" s="11" t="s">
-        <v>135</v>
+    <row r="180" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A180" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B180" s="2">
         <v>0.05</v>
@@ -14403,9 +13050,9 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="181" spans="1:22" ht="16">
-      <c r="A181" s="2" t="s">
-        <v>136</v>
+    <row r="181" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A181" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B181" s="2">
         <v>0.16389999999999999</v>
@@ -14471,9 +13118,9 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="182" spans="1:22">
-      <c r="A182" s="2" t="s">
-        <v>137</v>
+    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A182" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B182" s="2">
         <v>0.1837</v>
@@ -14539,9 +13186,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="183" spans="1:22">
-      <c r="A183" s="2" t="s">
-        <v>138</v>
+    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A183" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B183" s="2">
         <v>9.0899999999999995E-2</v>
@@ -14607,9 +13254,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:22" ht="15">
-      <c r="A184" s="10" t="s">
-        <v>139</v>
+    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A184" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B184" s="2">
         <v>0</v>
@@ -14675,9 +13322,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:22">
-      <c r="A185" s="2" t="s">
-        <v>140</v>
+    <row r="185" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A185" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B185" s="2">
         <v>0.15629999999999999</v>
@@ -14743,9 +13390,9 @@
         <v>13.07</v>
       </c>
     </row>
-    <row r="186" spans="1:22">
-      <c r="A186" s="2" t="s">
-        <v>140</v>
+    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A186" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B186" s="2">
         <v>0.15629999999999999</v>
@@ -14811,9 +13458,9 @@
         <v>10.17</v>
       </c>
     </row>
-    <row r="187" spans="1:22">
-      <c r="A187" s="2" t="s">
-        <v>141</v>
+    <row r="187" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A187" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B187" s="2">
         <v>0.2</v>
@@ -14879,9 +13526,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:22">
-      <c r="A188" s="2" t="s">
-        <v>141</v>
+    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A188" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B188" s="2">
         <v>0.2</v>
@@ -14947,9 +13594,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="189" spans="1:22">
-      <c r="A189" s="2" t="s">
-        <v>141</v>
+    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A189" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B189" s="2">
         <v>0.2</v>
@@ -15015,9 +13662,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="190" spans="1:22">
-      <c r="A190" s="2" t="s">
-        <v>141</v>
+    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A190" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B190" s="2">
         <v>0.2</v>
@@ -15083,9 +13730,9 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="191" spans="1:22">
-      <c r="A191" s="2" t="s">
-        <v>141</v>
+    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A191" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B191" s="2">
         <v>0.2</v>
@@ -15151,9 +13798,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:22" ht="16">
-      <c r="A192" s="2" t="s">
-        <v>142</v>
+    <row r="192" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A192" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B192" s="2">
         <v>0.16400000000000001</v>
@@ -15219,9 +13866,9 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="193" spans="1:22" ht="16">
-      <c r="A193" s="2" t="s">
-        <v>143</v>
+    <row r="193" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A193" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B193" s="2">
         <v>0.16400000000000001</v>
@@ -15287,9 +13934,9 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="194" spans="1:22" ht="16">
-      <c r="A194" s="2" t="s">
-        <v>144</v>
+    <row r="194" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A194" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B194" s="2">
         <v>0.13900000000000001</v>
@@ -15355,9 +14002,9 @@
         <v>8.4</v>
       </c>
     </row>
-    <row r="195" spans="1:22" ht="16">
-      <c r="A195" s="2" t="s">
-        <v>145</v>
+    <row r="195" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A195" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B195" s="2">
         <v>0.16300000000000001</v>
@@ -15423,9 +14070,9 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="196" spans="1:22" ht="16">
-      <c r="A196" s="2" t="s">
-        <v>146</v>
+    <row r="196" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A196" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B196" s="2">
         <v>0.16300000000000001</v>
@@ -15491,9 +14138,9 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="197" spans="1:22" ht="16">
-      <c r="A197" s="2" t="s">
-        <v>147</v>
+    <row r="197" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A197" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B197" s="2">
         <v>0.154</v>
@@ -15559,9 +14206,9 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="198" spans="1:22" ht="16">
-      <c r="A198" s="2" t="s">
-        <v>148</v>
+    <row r="198" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A198" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B198" s="2">
         <v>0.154</v>
@@ -15627,9 +14274,9 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="199" spans="1:22">
-      <c r="A199" s="2" t="s">
-        <v>149</v>
+    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A199" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B199" s="2">
         <v>0.06</v>
@@ -15695,9 +14342,9 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="200" spans="1:22">
-      <c r="A200" s="2" t="s">
-        <v>149</v>
+    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A200" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B200" s="2">
         <v>0.06</v>
@@ -15763,9 +14410,9 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="201" spans="1:22">
-      <c r="A201" s="2" t="s">
-        <v>149</v>
+    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A201" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B201" s="2">
         <v>0.06</v>
@@ -15831,9 +14478,9 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="202" spans="1:22">
-      <c r="A202" s="2" t="s">
-        <v>149</v>
+    <row r="202" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A202" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B202" s="2">
         <v>0.06</v>
@@ -15899,9 +14546,9 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="203" spans="1:22">
-      <c r="A203" s="2" t="s">
-        <v>149</v>
+    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A203" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B203" s="2">
         <v>0.06</v>
@@ -15967,9 +14614,9 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="204" spans="1:22" ht="16">
-      <c r="A204" s="2" t="s">
-        <v>150</v>
+    <row r="204" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A204" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B204" s="2">
         <v>0.06</v>
@@ -16035,9 +14682,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="1:22" ht="16">
-      <c r="A205" s="2" t="s">
-        <v>150</v>
+    <row r="205" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A205" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B205" s="2">
         <v>0.06</v>
@@ -16103,9 +14750,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="206" spans="1:22" ht="16">
-      <c r="A206" s="2" t="s">
-        <v>151</v>
+    <row r="206" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A206" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B206" s="2">
         <v>0.11</v>
@@ -16171,9 +14818,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="207" spans="1:22" ht="16">
-      <c r="A207" s="2" t="s">
-        <v>151</v>
+    <row r="207" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A207" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B207" s="2">
         <v>0.11</v>
@@ -16239,9 +14886,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="208" spans="1:22" ht="16">
-      <c r="A208" s="2" t="s">
-        <v>152</v>
+    <row r="208" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A208" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B208" s="2">
         <v>0.13</v>
@@ -16307,9 +14954,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="209" spans="1:22" ht="16">
-      <c r="A209" s="2" t="s">
-        <v>153</v>
+    <row r="209" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A209" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B209" s="2">
         <v>0.15</v>
@@ -16375,9 +15022,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:22">
-      <c r="A210" s="2" t="s">
-        <v>154</v>
+    <row r="210" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A210" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B210" s="2">
         <v>0.06</v>
@@ -16443,9 +15090,9 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="211" spans="1:22" ht="16">
-      <c r="A211" s="2" t="s">
-        <v>155</v>
+    <row r="211" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A211" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B211" s="2">
         <v>7.8E-2</v>
@@ -16511,9 +15158,9 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="212" spans="1:22" ht="16">
-      <c r="A212" s="2" t="s">
-        <v>156</v>
+    <row r="212" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A212" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B212" s="2">
         <v>0.05</v>
@@ -16579,9 +15226,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="213" spans="1:22" ht="16">
-      <c r="A213" s="2" t="s">
-        <v>157</v>
+    <row r="213" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A213" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B213" s="2">
         <v>0.1585</v>
@@ -16647,9 +15294,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="214" spans="1:22" ht="18">
-      <c r="A214" s="2" t="s">
-        <v>158</v>
+    <row r="214" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A214" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B214" s="2">
         <v>3.6999999999999998E-2</v>
@@ -16715,9 +15362,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="215" spans="1:22" ht="18">
-      <c r="A215" s="2" t="s">
-        <v>158</v>
+    <row r="215" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A215" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B215" s="2">
         <v>3.6999999999999998E-2</v>
@@ -16783,9 +15430,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="216" spans="1:22" ht="18">
-      <c r="A216" s="2" t="s">
-        <v>158</v>
+    <row r="216" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A216" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B216" s="2">
         <v>3.6999999999999998E-2</v>
@@ -16851,9 +15498,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="217" spans="1:22">
-      <c r="A217" s="2" t="s">
-        <v>159</v>
+    <row r="217" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A217" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B217" s="2">
         <v>0.17</v>
@@ -16919,9 +15566,9 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:22">
-      <c r="A218" s="2" t="s">
-        <v>159</v>
+    <row r="218" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A218" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B218" s="2">
         <v>0.17</v>
@@ -16987,9 +15634,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" spans="1:22">
-      <c r="A219" s="2" t="s">
-        <v>159</v>
+    <row r="219" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A219" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B219" s="2">
         <v>0.17</v>
@@ -17055,9 +15702,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="220" spans="1:22">
-      <c r="A220" s="2" t="s">
-        <v>159</v>
+    <row r="220" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A220" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B220" s="2">
         <v>0.17</v>
@@ -17123,9 +15770,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:22" ht="16">
-      <c r="A221" s="2" t="s">
-        <v>160</v>
+    <row r="221" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A221" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B221" s="2">
         <v>0.1</v>
@@ -17191,9 +15838,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" spans="1:22" ht="16">
-      <c r="A222" s="2" t="s">
-        <v>161</v>
+    <row r="222" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A222" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B222" s="2">
         <v>0.08</v>
@@ -17259,9 +15906,9 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:22" ht="16">
-      <c r="A223" s="2" t="s">
-        <v>162</v>
+    <row r="223" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A223" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B223" s="2">
         <v>0.06</v>
@@ -17327,9 +15974,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:22" ht="16">
-      <c r="A224" s="2" t="s">
-        <v>163</v>
+    <row r="224" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A224" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B224" s="2">
         <v>0.04</v>
@@ -17395,9 +16042,9 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="225" spans="1:22" ht="16">
-      <c r="A225" s="2" t="s">
-        <v>164</v>
+    <row r="225" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A225" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B225" s="2">
         <v>9.2600000000000002E-2</v>
@@ -17463,9 +16110,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:22">
-      <c r="A226" s="2" t="s">
-        <v>165</v>
+    <row r="226" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A226" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B226" s="2">
         <v>4.5499999999999999E-2</v>
@@ -17531,9 +16178,9 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="227" spans="1:22">
-      <c r="A227" s="2" t="s">
-        <v>166</v>
+    <row r="227" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A227" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B227" s="2">
         <v>4.3499999999999997E-2</v>
@@ -17599,9 +16246,9 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="228" spans="1:22">
-      <c r="A228" s="2" t="s">
-        <v>167</v>
+    <row r="228" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A228" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B228" s="2">
         <v>0.12330000000000001</v>
@@ -17667,9 +16314,9 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="229" spans="1:22" ht="16">
-      <c r="A229" s="2" t="s">
-        <v>168</v>
+    <row r="229" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A229" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B229" s="2">
         <v>0.08</v>
@@ -17735,9 +16382,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="230" spans="1:22" ht="16">
-      <c r="A230" s="2" t="s">
-        <v>168</v>
+    <row r="230" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A230" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B230" s="2">
         <v>0.08</v>
@@ -17803,9 +16450,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:22" ht="16">
-      <c r="A231" s="2" t="s">
-        <v>168</v>
+    <row r="231" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A231" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B231" s="2">
         <v>0.08</v>
@@ -17871,9 +16518,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:22" ht="16">
-      <c r="A232" s="2" t="s">
-        <v>169</v>
+    <row r="232" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A232" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B232" s="2">
         <v>0.1</v>
@@ -17939,9 +16586,9 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="233" spans="1:22" ht="16">
-      <c r="A233" s="2" t="s">
-        <v>169</v>
+    <row r="233" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A233" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B233" s="2">
         <v>0.1</v>
@@ -18007,9 +16654,9 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="234" spans="1:22" ht="16">
-      <c r="A234" s="2" t="s">
-        <v>169</v>
+    <row r="234" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A234" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B234" s="2">
         <v>0.1</v>
@@ -18075,9 +16722,9 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="235" spans="1:22" ht="16">
-      <c r="A235" s="2" t="s">
-        <v>169</v>
+    <row r="235" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A235" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B235" s="2">
         <v>0.1</v>
@@ -18143,9 +16790,9 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="236" spans="1:22">
-      <c r="A236" s="2" t="s">
-        <v>86</v>
+    <row r="236" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A236" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B236" s="2">
         <v>0.1111</v>
@@ -18211,9 +16858,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:22">
-      <c r="A237" s="2" t="s">
-        <v>170</v>
+    <row r="237" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A237" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B237" s="2">
         <v>0.10979999999999999</v>
@@ -18279,9 +16926,9 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="238" spans="1:22">
-      <c r="A238" s="2" t="s">
-        <v>171</v>
+    <row r="238" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A238" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B238" s="2">
         <v>0.1069</v>
@@ -18347,9 +16994,9 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="239" spans="1:22">
-      <c r="A239" s="2" t="s">
-        <v>172</v>
+    <row r="239" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A239" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B239" s="2">
         <v>0.1041</v>
@@ -18415,9 +17062,9 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="240" spans="1:22">
-      <c r="A240" s="2" t="s">
-        <v>173</v>
+    <row r="240" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A240" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B240" s="2">
         <v>0.10150000000000001</v>
@@ -18483,9 +17130,9 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="241" spans="1:22">
-      <c r="A241" s="2" t="s">
-        <v>174</v>
+    <row r="241" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A241" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B241" s="2">
         <v>9.9099999999999994E-2</v>
@@ -18551,9 +17198,9 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="242" spans="1:22" ht="16">
-      <c r="A242" s="2" t="s">
-        <v>175</v>
+    <row r="242" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A242" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B242" s="2">
         <v>0.1</v>
@@ -18619,9 +17266,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="243" spans="1:22" ht="16">
-      <c r="A243" s="2" t="s">
-        <v>175</v>
+    <row r="243" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A243" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B243" s="2">
         <v>0.1</v>
@@ -18687,9 +17334,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="244" spans="1:22" ht="16">
-      <c r="A244" s="2" t="s">
-        <v>175</v>
+    <row r="244" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A244" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B244" s="2">
         <v>0.1</v>
@@ -18755,9 +17402,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="245" spans="1:22" ht="16">
-      <c r="A245" s="2" t="s">
-        <v>175</v>
+    <row r="245" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A245" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B245" s="2">
         <v>0.1</v>
@@ -18823,9 +17470,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="246" spans="1:22" ht="16">
-      <c r="A246" s="2" t="s">
-        <v>176</v>
+    <row r="246" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A246" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B246" s="2">
         <v>0.16</v>
@@ -18891,9 +17538,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:22">
-      <c r="A247" s="2" t="s">
-        <v>177</v>
+    <row r="247" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A247" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B247" s="2">
         <v>0.04</v>
@@ -18959,9 +17606,9 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="248" spans="1:22">
-      <c r="A248" s="2" t="s">
-        <v>177</v>
+    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A248" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B248" s="2">
         <v>0.04</v>
@@ -19027,9 +17674,9 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="249" spans="1:22" ht="16">
-      <c r="A249" s="2" t="s">
-        <v>178</v>
+    <row r="249" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A249" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B249" s="2">
         <v>0.1099</v>
@@ -19095,9 +17742,9 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="250" spans="1:22" ht="16">
-      <c r="A250" s="2" t="s">
-        <v>178</v>
+    <row r="250" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A250" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B250" s="2">
         <v>0.1099</v>
@@ -19163,9 +17810,9 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="251" spans="1:22" ht="16">
-      <c r="A251" s="2" t="s">
-        <v>179</v>
+    <row r="251" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A251" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B251" s="2">
         <v>0.03</v>
@@ -19231,9 +17878,9 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="252" spans="1:22" ht="16">
-      <c r="A252" s="2" t="s">
-        <v>180</v>
+    <row r="252" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A252" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B252" s="2">
         <v>0.1489</v>
@@ -19299,9 +17946,9 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="253" spans="1:22" ht="16">
-      <c r="A253" s="2" t="s">
-        <v>141</v>
+    <row r="253" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A253" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B253" s="2">
         <v>0.16669999999999999</v>
@@ -19367,9 +18014,9 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="254" spans="1:22" ht="16">
-      <c r="A254" s="2" t="s">
-        <v>141</v>
+    <row r="254" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A254" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B254" s="2">
         <v>0.16669999999999999</v>
@@ -19435,9 +18082,9 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="255" spans="1:22" ht="16">
-      <c r="A255" s="2" t="s">
-        <v>141</v>
+    <row r="255" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A255" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B255" s="2">
         <v>0.16669999999999999</v>
@@ -19503,9 +18150,9 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="256" spans="1:22" ht="16">
-      <c r="A256" s="2" t="s">
-        <v>181</v>
+    <row r="256" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A256" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B256" s="2">
         <v>0.13039999999999999</v>
@@ -19571,9 +18218,9 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="257" spans="1:22" ht="16">
-      <c r="A257" s="2" t="s">
-        <v>181</v>
+    <row r="257" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A257" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B257" s="2">
         <v>0.13039999999999999</v>
@@ -19639,9 +18286,9 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="258" spans="1:22" ht="16">
-      <c r="A258" s="2" t="s">
-        <v>181</v>
+    <row r="258" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A258" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B258" s="2">
         <v>0.13039999999999999</v>
@@ -19707,9 +18354,9 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="259" spans="1:22" ht="16">
-      <c r="A259" s="2" t="s">
-        <v>181</v>
+    <row r="259" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A259" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B259" s="2">
         <v>0.13039999999999999</v>
@@ -19775,9 +18422,9 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="260" spans="1:22" ht="16">
-      <c r="A260" s="2" t="s">
-        <v>181</v>
+    <row r="260" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A260" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B260" s="2">
         <v>0.13039999999999999</v>
@@ -19843,9 +18490,9 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="261" spans="1:22" ht="16">
-      <c r="A261" s="2" t="s">
-        <v>181</v>
+    <row r="261" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A261" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B261" s="2">
         <v>0.13039999999999999</v>
@@ -19911,9 +18558,9 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="262" spans="1:22" ht="16">
-      <c r="A262" s="2" t="s">
-        <v>181</v>
+    <row r="262" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A262" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B262" s="2">
         <v>0.13039999999999999</v>
@@ -19979,9 +18626,9 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="263" spans="1:22" ht="16">
-      <c r="A263" s="2" t="s">
-        <v>182</v>
+    <row r="263" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A263" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B263" s="2">
         <v>0.16389999999999999</v>
@@ -20047,9 +18694,9 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="264" spans="1:22" ht="16">
-      <c r="A264" s="2" t="s">
-        <v>182</v>
+    <row r="264" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A264" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B264" s="2">
         <v>0.16389999999999999</v>
@@ -20115,9 +18762,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="265" spans="1:22" ht="16">
-      <c r="A265" s="2" t="s">
-        <v>182</v>
+    <row r="265" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A265" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B265" s="2">
         <v>0.16389999999999999</v>
@@ -20183,9 +18830,9 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="266" spans="1:22" ht="16">
-      <c r="A266" s="2" t="s">
-        <v>182</v>
+    <row r="266" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A266" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B266" s="2">
         <v>0.16389999999999999</v>
@@ -20251,9 +18898,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="267" spans="1:22" ht="16">
-      <c r="A267" s="2" t="s">
-        <v>182</v>
+    <row r="267" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A267" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B267" s="2">
         <v>0.16389999999999999</v>
@@ -20319,9 +18966,9 @@
         <v>24</v>
       </c>
     </row>
-    <row r="268" spans="1:22" ht="16">
-      <c r="A268" s="2" t="s">
-        <v>183</v>
+    <row r="268" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A268" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B268" s="2">
         <v>0.19</v>
@@ -20387,9 +19034,9 @@
         <v>24.24</v>
       </c>
     </row>
-    <row r="269" spans="1:22" ht="16">
-      <c r="A269" s="2" t="s">
-        <v>183</v>
+    <row r="269" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A269" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B269" s="2">
         <v>0.19</v>
@@ -20455,9 +19102,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="270" spans="1:22" ht="16">
-      <c r="A270" s="2" t="s">
-        <v>183</v>
+    <row r="270" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A270" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B270" s="2">
         <v>0.19</v>
@@ -20523,9 +19170,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:22" ht="16">
-      <c r="A271" s="2" t="s">
-        <v>38</v>
+    <row r="271" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A271" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B271" s="2">
         <v>0.19</v>
@@ -20591,9 +19238,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="272" spans="1:22" ht="16">
-      <c r="A272" s="2" t="s">
-        <v>38</v>
+    <row r="272" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A272" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B272" s="2">
         <v>0.19</v>
@@ -20659,9 +19306,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="273" spans="1:22" ht="16">
-      <c r="A273" s="2" t="s">
-        <v>184</v>
+    <row r="273" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A273" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B273" s="2">
         <v>0.22450000000000001</v>
@@ -20727,9 +19374,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="274" spans="1:22" ht="16">
-      <c r="A274" s="2" t="s">
-        <v>184</v>
+    <row r="274" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A274" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B274" s="2">
         <v>0.22450000000000001</v>
@@ -20795,9 +19442,9 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="275" spans="1:22" ht="16">
-      <c r="A275" s="2" t="s">
-        <v>184</v>
+    <row r="275" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A275" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B275" s="2">
         <v>0.22450000000000001</v>
@@ -20863,9 +19510,9 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="276" spans="1:22" ht="16">
-      <c r="A276" s="2" t="s">
-        <v>184</v>
+    <row r="276" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A276" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B276" s="2">
         <v>0.22450000000000001</v>
@@ -20931,9 +19578,9 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="277" spans="1:22" ht="16">
-      <c r="A277" s="2" t="s">
-        <v>184</v>
+    <row r="277" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A277" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B277" s="2">
         <v>0.22450000000000001</v>
@@ -20999,9 +19646,9 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="278" spans="1:22" ht="16">
-      <c r="A278" s="2" t="s">
-        <v>184</v>
+    <row r="278" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A278" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B278" s="2">
         <v>0.22450000000000001</v>
@@ -21067,9 +19714,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="279" spans="1:22" ht="18">
-      <c r="A279" s="2" t="s">
-        <v>22</v>
+    <row r="279" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A279" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B279" s="2">
         <v>0.16389999999999999</v>
@@ -21135,9 +19782,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="280" spans="1:22" ht="18">
-      <c r="A280" s="2" t="s">
-        <v>22</v>
+    <row r="280" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A280" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B280" s="2">
         <v>0.16389999999999999</v>
@@ -21203,9 +19850,9 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="281" spans="1:22" ht="18">
-      <c r="A281" s="2" t="s">
-        <v>22</v>
+    <row r="281" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A281" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B281" s="2">
         <v>0.16389999999999999</v>
@@ -21271,9 +19918,9 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="282" spans="1:22" ht="18">
-      <c r="A282" s="2" t="s">
-        <v>22</v>
+    <row r="282" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A282" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B282" s="2">
         <v>0.16389999999999999</v>
@@ -21339,9 +19986,9 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="283" spans="1:22" ht="18">
-      <c r="A283" s="2" t="s">
-        <v>22</v>
+    <row r="283" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A283" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B283" s="2">
         <v>0.16389999999999999</v>
@@ -21407,9 +20054,9 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="18">
-      <c r="A284" s="2" t="s">
-        <v>22</v>
+    <row r="284" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A284" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B284" s="2">
         <v>0.16389999999999999</v>
@@ -21475,9 +20122,9 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="285" spans="1:22" ht="18">
-      <c r="A285" s="2" t="s">
-        <v>22</v>
+    <row r="285" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A285" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B285" s="2">
         <v>0.16389999999999999</v>
@@ -21543,9 +20190,9 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="286" spans="1:22" ht="18">
-      <c r="A286" s="2" t="s">
-        <v>22</v>
+    <row r="286" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A286" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B286" s="2">
         <v>0.16389999999999999</v>
@@ -21611,9 +20258,9 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="287" spans="1:22">
-      <c r="A287" s="2" t="s">
-        <v>185</v>
+    <row r="287" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A287" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B287" s="2">
         <v>6.9800000000000001E-2</v>
@@ -21679,9 +20326,9 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="288" spans="1:22">
-      <c r="A288" s="2" t="s">
-        <v>185</v>
+    <row r="288" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A288" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B288" s="2">
         <v>6.9800000000000001E-2</v>
@@ -21747,9 +20394,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="289" spans="1:22">
-      <c r="A289" s="2" t="s">
-        <v>185</v>
+    <row r="289" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A289" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B289" s="2">
         <v>6.9800000000000001E-2</v>
@@ -21815,9 +20462,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="290" spans="1:22" ht="16">
-      <c r="A290" s="2" t="s">
-        <v>186</v>
+    <row r="290" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A290" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B290" s="2">
         <v>9.0899999999999995E-2</v>
@@ -21883,9 +20530,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="291" spans="1:22" ht="16">
-      <c r="A291" s="2" t="s">
-        <v>186</v>
+    <row r="291" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A291" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B291" s="2">
         <v>9.0899999999999995E-2</v>
@@ -21951,9 +20598,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="292" spans="1:22" ht="16">
-      <c r="A292" s="2" t="s">
-        <v>186</v>
+    <row r="292" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A292" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B292" s="2">
         <v>9.0899999999999995E-2</v>
@@ -22019,9 +20666,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="293" spans="1:22" ht="16">
-      <c r="A293" s="2" t="s">
-        <v>22</v>
+    <row r="293" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A293" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B293" s="2">
         <v>0.16389999999999999</v>
@@ -22087,9 +20734,9 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="294" spans="1:22" ht="16">
-      <c r="A294" s="2" t="s">
-        <v>22</v>
+    <row r="294" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A294" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B294" s="2">
         <v>0.16389999999999999</v>
@@ -22155,9 +20802,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="295" spans="1:22" ht="16">
-      <c r="A295" s="2" t="s">
-        <v>22</v>
+    <row r="295" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A295" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B295" s="2">
         <v>0.16389999999999999</v>
@@ -22223,9 +20870,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="296" spans="1:22" ht="16">
-      <c r="A296" s="2" t="s">
-        <v>187</v>
+    <row r="296" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A296" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B296" s="2">
         <v>7.4999999999999997E-2</v>
@@ -22291,9 +20938,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="297" spans="1:22" ht="16">
-      <c r="A297" s="2" t="s">
-        <v>187</v>
+    <row r="297" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A297" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B297" s="2">
         <v>7.4999999999999997E-2</v>
@@ -22359,9 +21006,9 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="298" spans="1:22" ht="21" customHeight="1">
-      <c r="A298" s="2" t="s">
-        <v>86</v>
+    <row r="298" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A298" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B298" s="2">
         <v>0.1111</v>
@@ -22427,9 +21074,9 @@
         <v>35.6</v>
       </c>
     </row>
-    <row r="299" spans="1:22" ht="21" customHeight="1">
-      <c r="A299" s="2" t="s">
-        <v>86</v>
+    <row r="299" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B299" s="2">
         <v>0.1111</v>
@@ -22495,9 +21142,9 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="300" spans="1:22" ht="21" customHeight="1">
-      <c r="A300" s="2" t="s">
-        <v>86</v>
+    <row r="300" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A300" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B300" s="2">
         <v>0.1111</v>
@@ -22563,9 +21210,9 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="301" spans="1:22" ht="21" customHeight="1">
-      <c r="A301" s="2" t="s">
-        <v>86</v>
+    <row r="301" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B301" s="2">
         <v>0.1111</v>
@@ -22631,9 +21278,9 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="302" spans="1:22" ht="21" customHeight="1">
-      <c r="A302" s="2" t="s">
-        <v>86</v>
+    <row r="302" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A302" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B302" s="2">
         <v>0.1111</v>
@@ -22699,9 +21346,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="303" spans="1:22" ht="16">
-      <c r="A303" s="2" t="s">
-        <v>188</v>
+    <row r="303" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A303" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B303" s="2">
         <v>0.1111</v>
@@ -22767,9 +21414,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:22" ht="16">
-      <c r="A304" s="2" t="s">
-        <v>188</v>
+    <row r="304" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A304" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B304" s="2">
         <v>0.1111</v>
@@ -22835,9 +21482,9 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="305" spans="1:22" ht="16">
-      <c r="A305" s="2" t="s">
-        <v>188</v>
+    <row r="305" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A305" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B305" s="2">
         <v>0.1111</v>
@@ -22903,9 +21550,9 @@
         <v>35.9</v>
       </c>
     </row>
-    <row r="306" spans="1:22" ht="16">
-      <c r="A306" s="2" t="s">
-        <v>188</v>
+    <row r="306" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A306" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B306" s="2">
         <v>0.1111</v>
@@ -22971,9 +21618,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="307" spans="1:22" ht="16">
-      <c r="A307" s="2" t="s">
-        <v>188</v>
+    <row r="307" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A307" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B307" s="2">
         <v>0.1111</v>
@@ -23039,9 +21686,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:22" ht="16">
-      <c r="A308" s="2" t="s">
-        <v>188</v>
+    <row r="308" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A308" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B308" s="2">
         <v>0.1111</v>
@@ -23107,9 +21754,9 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="309" spans="1:22" ht="16">
-      <c r="A309" s="2" t="s">
-        <v>188</v>
+    <row r="309" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A309" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B309" s="2">
         <v>0.1111</v>
@@ -23175,9 +21822,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:22" ht="16">
-      <c r="A310" s="2" t="s">
-        <v>189</v>
+    <row r="310" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A310" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B310" s="2">
         <v>0.1489</v>
@@ -23243,9 +21890,9 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="311" spans="1:22" ht="16">
-      <c r="A311" s="2" t="s">
-        <v>189</v>
+    <row r="311" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A311" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B311" s="2">
         <v>0.1489</v>
@@ -23311,9 +21958,9 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="312" spans="1:22" ht="16">
-      <c r="A312" s="2" t="s">
-        <v>189</v>
+    <row r="312" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A312" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B312" s="2">
         <v>0.1489</v>
@@ -23379,9 +22026,9 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="313" spans="1:22" ht="16">
-      <c r="A313" s="2" t="s">
-        <v>180</v>
+    <row r="313" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A313" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B313" s="2">
         <v>0.1489</v>
@@ -23447,9 +22094,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="314" spans="1:22">
-      <c r="A314" s="2" t="s">
-        <v>190</v>
+    <row r="314" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A314" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B314" s="2">
         <v>0.19750000000000001</v>
@@ -23515,9 +22162,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:22">
-      <c r="A315" s="2" t="s">
-        <v>191</v>
+    <row r="315" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A315" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B315" s="2">
         <v>0.16</v>
@@ -23583,9 +22230,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="316" spans="1:22">
-      <c r="A316" s="2" t="s">
-        <v>192</v>
+    <row r="316" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A316" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B316" s="2">
         <v>0.16</v>
@@ -23651,9 +22298,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:22">
-      <c r="A317" s="2" t="s">
-        <v>193</v>
+    <row r="317" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A317" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B317" s="2">
         <v>0.19750000000000001</v>
@@ -23719,9 +22366,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="318" spans="1:22">
-      <c r="A318" s="2" t="s">
-        <v>194</v>
+    <row r="318" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A318" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B318" s="2">
         <v>0.16</v>
@@ -23787,9 +22434,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:22">
-      <c r="A319" s="2" t="s">
-        <v>192</v>
+    <row r="319" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A319" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B319" s="2">
         <v>0.16</v>
@@ -23855,9 +22502,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="320" spans="1:22">
-      <c r="A320" s="2" t="s">
-        <v>195</v>
+    <row r="320" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A320" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B320" s="2">
         <v>0.16</v>
@@ -23923,9 +22570,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="321" spans="1:22">
-      <c r="A321" s="2" t="s">
-        <v>193</v>
+    <row r="321" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A321" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B321" s="2">
         <v>0.19750000000000001</v>
@@ -23991,9 +22638,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:22">
-      <c r="A322" s="2" t="s">
-        <v>191</v>
+    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A322" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B322" s="2">
         <v>0.16</v>
@@ -24059,9 +22706,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="323" spans="1:22">
-      <c r="A323" s="2" t="s">
-        <v>192</v>
+    <row r="323" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A323" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B323" s="2">
         <v>0.16</v>
@@ -24127,9 +22774,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:22">
-      <c r="A324" s="2" t="s">
-        <v>195</v>
+    <row r="324" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A324" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B324" s="2">
         <v>0.16</v>
@@ -24195,9 +22842,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="325" spans="1:22" ht="16">
-      <c r="A325" s="2" t="s">
-        <v>196</v>
+    <row r="325" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A325" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B325" s="2">
         <v>6.8199999999999997E-2</v>
@@ -24263,9 +22910,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="326" spans="1:22" ht="16">
-      <c r="A326" s="2" t="s">
-        <v>197</v>
+    <row r="326" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A326" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B326" s="2">
         <v>6.6699999999999995E-2</v>
@@ -24331,9 +22978,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="327" spans="1:22" ht="16">
-      <c r="A327" s="2" t="s">
-        <v>198</v>
+    <row r="327" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A327" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B327" s="2">
         <v>6.5199999999999994E-2</v>
@@ -24399,9 +23046,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="328" spans="1:22" ht="16">
-      <c r="A328" s="2" t="s">
-        <v>199</v>
+    <row r="328" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A328" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B328" s="2">
         <v>6.3799999999999996E-2</v>
@@ -24467,9 +23114,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="329" spans="1:22" ht="16">
-      <c r="A329" s="2" t="s">
-        <v>200</v>
+    <row r="329" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A329" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B329" s="2">
         <v>6.25E-2</v>
@@ -24535,9 +23182,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:22" ht="16">
-      <c r="A330" s="2" t="s">
-        <v>185</v>
+    <row r="330" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A330" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B330" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24603,9 +23250,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="331" spans="1:22" ht="16">
-      <c r="A331" s="2" t="s">
-        <v>201</v>
+    <row r="331" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A331" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B331" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24671,9 +23318,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="332" spans="1:22">
-      <c r="A332" s="2" t="s">
-        <v>201</v>
+    <row r="332" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A332" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B332" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24739,9 +23386,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="333" spans="1:22">
-      <c r="A333" s="2" t="s">
-        <v>201</v>
+    <row r="333" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A333" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B333" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24807,9 +23454,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="334" spans="1:22">
-      <c r="A334" s="2" t="s">
-        <v>201</v>
+    <row r="334" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A334" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B334" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24875,9 +23522,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="335" spans="1:22">
-      <c r="A335" s="2" t="s">
-        <v>201</v>
+    <row r="335" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A335" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B335" s="2">
         <v>6.9800000000000001E-2</v>
@@ -24943,9 +23590,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="336" spans="1:22">
-      <c r="A336" s="2" t="s">
-        <v>202</v>
+    <row r="336" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A336" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B336" s="2">
         <v>4.7600000000000003E-2</v>
@@ -25011,9 +23658,9 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="337" spans="1:22">
-      <c r="A337" s="2" t="s">
-        <v>202</v>
+    <row r="337" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A337" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B337" s="2">
         <v>4.7600000000000003E-2</v>
@@ -25079,9 +23726,9 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="338" spans="1:22">
-      <c r="A338" s="2" t="s">
-        <v>202</v>
+    <row r="338" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A338" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B338" s="2">
         <v>4.7600000000000003E-2</v>
@@ -25147,9 +23794,9 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="339" spans="1:22">
-      <c r="A339" s="2" t="s">
-        <v>202</v>
+    <row r="339" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A339" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B339" s="2">
         <v>4.7600000000000003E-2</v>
@@ -25215,9 +23862,9 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="340" spans="1:22">
-      <c r="A340" s="2" t="s">
-        <v>202</v>
+    <row r="340" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A340" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B340" s="2">
         <v>4.7600000000000003E-2</v>
@@ -25283,9 +23930,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="341" spans="1:22">
-      <c r="A341" s="2" t="s">
-        <v>203</v>
+    <row r="341" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A341" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B341" s="2">
         <v>0.2</v>
@@ -25351,9 +23998,9 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="342" spans="1:22" ht="18">
-      <c r="A342" s="2" t="s">
-        <v>86</v>
+    <row r="342" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A342" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B342" s="2">
         <v>0.1111</v>
@@ -25419,9 +24066,9 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="343" spans="1:22" ht="18">
-      <c r="A343" s="2" t="s">
-        <v>86</v>
+    <row r="343" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A343" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B343" s="2">
         <v>0.1111</v>
@@ -25487,9 +24134,9 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="344" spans="1:22" ht="18">
-      <c r="A344" s="2" t="s">
-        <v>86</v>
+    <row r="344" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A344" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B344" s="2">
         <v>0.1111</v>
@@ -25555,9 +24202,9 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="345" spans="1:22">
-      <c r="A345" s="2" t="s">
-        <v>204</v>
+    <row r="345" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A345" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B345" s="2">
         <v>0.1011</v>
@@ -25623,9 +24270,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:22">
-      <c r="A346" s="2" t="s">
-        <v>204</v>
+    <row r="346" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A346" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B346" s="2">
         <v>0.1011</v>
@@ -25691,9 +24338,9 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="347" spans="1:22">
-      <c r="A347" s="2" t="s">
-        <v>204</v>
+    <row r="347" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A347" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B347" s="2">
         <v>0.1011</v>
@@ -25759,9 +24406,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="348" spans="1:22">
-      <c r="A348" s="2" t="s">
-        <v>204</v>
+    <row r="348" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A348" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B348" s="2">
         <v>0.1011</v>
@@ -25827,9 +24474,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="349" spans="1:22">
-      <c r="A349" s="2" t="s">
-        <v>204</v>
+    <row r="349" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A349" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B349" s="2">
         <v>0.1011</v>
@@ -25895,9 +24542,9 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="350" spans="1:22">
-      <c r="A350" s="2" t="s">
-        <v>204</v>
+    <row r="350" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A350" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B350" s="2">
         <v>0.1011</v>
@@ -25963,9 +24610,9 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="351" spans="1:22">
-      <c r="A351" s="2" t="s">
-        <v>204</v>
+    <row r="351" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A351" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B351" s="2">
         <v>0.1011</v>
@@ -26031,9 +24678,9 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="352" spans="1:22">
-      <c r="A352" s="2" t="s">
-        <v>181</v>
+    <row r="352" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A352" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B352" s="2">
         <v>0.13039999999999999</v>
@@ -26099,9 +24746,9 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="353" spans="1:22">
-      <c r="A353" s="2" t="s">
-        <v>181</v>
+    <row r="353" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A353" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B353" s="2">
         <v>0.13039999999999999</v>
@@ -26167,9 +24814,9 @@
         <v>29.8</v>
       </c>
     </row>
-    <row r="354" spans="1:22">
-      <c r="A354" s="2" t="s">
-        <v>205</v>
+    <row r="354" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A354" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B354" s="2">
         <v>0.125</v>
@@ -26235,9 +24882,9 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="355" spans="1:22">
-      <c r="A355" s="2" t="s">
-        <v>206</v>
+    <row r="355" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A355" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B355" s="2">
         <v>0.125</v>
@@ -26303,9 +24950,9 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="356" spans="1:22">
-      <c r="A356" s="2" t="s">
-        <v>207</v>
+    <row r="356" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A356" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B356" s="2">
         <v>0.1429</v>
@@ -26371,9 +25018,9 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="357" spans="1:22">
-      <c r="A357" s="2" t="s">
-        <v>208</v>
+    <row r="357" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A357" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B357" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26439,9 +25086,9 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="358" spans="1:22">
-      <c r="A358" s="2" t="s">
-        <v>208</v>
+    <row r="358" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A358" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B358" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26507,9 +25154,9 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="359" spans="1:22">
-      <c r="A359" s="2" t="s">
-        <v>208</v>
+    <row r="359" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A359" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B359" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26575,9 +25222,9 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="360" spans="1:22">
-      <c r="A360" s="2" t="s">
-        <v>208</v>
+    <row r="360" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A360" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B360" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26643,9 +25290,9 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="361" spans="1:22">
-      <c r="A361" s="2" t="s">
-        <v>208</v>
+    <row r="361" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A361" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B361" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26711,9 +25358,9 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="362" spans="1:22">
-      <c r="A362" s="2" t="s">
-        <v>208</v>
+    <row r="362" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A362" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B362" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26779,9 +25426,9 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="363" spans="1:22">
-      <c r="A363" s="2" t="s">
-        <v>208</v>
+    <row r="363" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A363" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B363" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26847,9 +25494,9 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="364" spans="1:22">
-      <c r="A364" s="2" t="s">
-        <v>208</v>
+    <row r="364" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A364" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B364" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26915,9 +25562,9 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="365" spans="1:22">
-      <c r="A365" s="2" t="s">
-        <v>208</v>
+    <row r="365" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A365" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B365" s="2">
         <v>8.3299999999999999E-2</v>
@@ -26983,9 +25630,9 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="366" spans="1:22" ht="16">
-      <c r="A366" s="2" t="s">
-        <v>209</v>
+    <row r="366" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A366" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B366" s="2">
         <v>0.16</v>
@@ -27051,9 +25698,9 @@
         <v>44.62</v>
       </c>
     </row>
-    <row r="367" spans="1:22" ht="16">
-      <c r="A367" s="2" t="s">
-        <v>209</v>
+    <row r="367" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A367" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B367" s="2">
         <v>0.16</v>
@@ -27119,9 +25766,9 @@
         <v>40.24</v>
       </c>
     </row>
-    <row r="368" spans="1:22">
-      <c r="A368" s="2" t="s">
-        <v>82</v>
+    <row r="368" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A368" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B368" s="2">
         <v>6.9800000000000001E-2</v>
@@ -27187,9 +25834,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="369" spans="1:22">
-      <c r="A369" s="2" t="s">
-        <v>210</v>
+    <row r="369" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A369" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B369" s="2">
         <v>6.9800000000000001E-2</v>
@@ -27255,9 +25902,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="370" spans="1:22">
-      <c r="A370" s="2" t="s">
-        <v>211</v>
+    <row r="370" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A370" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B370" s="2">
         <v>6.9800000000000001E-2</v>
@@ -27323,9 +25970,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="371" spans="1:22">
-      <c r="A371" s="2" t="s">
-        <v>212</v>
+    <row r="371" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A371" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B371" s="2">
         <v>6.9800000000000001E-2</v>
@@ -27391,9 +26038,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="372" spans="1:22">
-      <c r="A372" s="2" t="s">
-        <v>181</v>
+    <row r="372" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A372" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B372" s="2">
         <v>0.13039999999999999</v>
@@ -27459,9 +26106,9 @@
         <v>47.96</v>
       </c>
     </row>
-    <row r="373" spans="1:22">
-      <c r="A373" s="2" t="s">
-        <v>213</v>
+    <row r="373" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A373" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B373" s="2">
         <v>0.23080000000000001</v>
@@ -27527,9 +26174,9 @@
         <v>21.26</v>
       </c>
     </row>
-    <row r="374" spans="1:22">
-      <c r="A374" s="2" t="s">
-        <v>181</v>
+    <row r="374" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A374" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B374" s="2">
         <v>0.13039999999999999</v>
@@ -27595,9 +26242,9 @@
         <v>25.28</v>
       </c>
     </row>
-    <row r="375" spans="1:22">
-      <c r="A375" s="2" t="s">
-        <v>213</v>
+    <row r="375" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A375" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B375" s="2">
         <v>0.23080000000000001</v>
@@ -27663,9 +26310,9 @@
         <v>18.05</v>
       </c>
     </row>
-    <row r="376" spans="1:22">
-      <c r="A376" s="2" t="s">
-        <v>214</v>
+    <row r="376" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A376" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B376" s="2">
         <v>0</v>
@@ -27731,9 +26378,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="377" spans="1:22">
-      <c r="A377" s="2" t="s">
-        <v>215</v>
+    <row r="377" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A377" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B377" s="2">
         <v>0.03</v>
@@ -27799,9 +26446,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="378" spans="1:22">
-      <c r="A378" s="2" t="s">
-        <v>216</v>
+    <row r="378" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A378" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B378" s="2">
         <v>0.05</v>
@@ -27867,9 +26514,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="379" spans="1:22">
-      <c r="A379" s="2" t="s">
-        <v>217</v>
+    <row r="379" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A379" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B379" s="2">
         <v>7.0000000000000007E-2</v>
@@ -27935,9 +26582,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="380" spans="1:22">
-      <c r="A380" s="2" t="s">
-        <v>218</v>
+    <row r="380" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A380" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B380" s="2">
         <v>0.09</v>
@@ -28003,9 +26650,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="381" spans="1:22">
-      <c r="A381" s="2" t="s">
-        <v>214</v>
+    <row r="381" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A381" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B381" s="2">
         <v>0</v>
@@ -28071,9 +26718,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="382" spans="1:22">
-      <c r="A382" s="2" t="s">
-        <v>215</v>
+    <row r="382" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A382" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B382" s="2">
         <v>0.03</v>
@@ -28139,9 +26786,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="383" spans="1:22">
-      <c r="A383" s="2" t="s">
-        <v>216</v>
+    <row r="383" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A383" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B383" s="2">
         <v>0.05</v>
@@ -28207,9 +26854,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="384" spans="1:22">
-      <c r="A384" s="2" t="s">
-        <v>217</v>
+    <row r="384" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A384" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B384" s="2">
         <v>7.0000000000000007E-2</v>
@@ -28275,9 +26922,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="385" spans="1:22">
-      <c r="A385" s="2" t="s">
-        <v>218</v>
+    <row r="385" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A385" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B385" s="2">
         <v>0.09</v>
@@ -28343,9 +26990,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="386" spans="1:22">
-      <c r="A386" s="2" t="s">
-        <v>219</v>
+    <row r="386" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A386" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B386" s="2">
         <v>0.12909999999999999</v>
@@ -28411,9 +27058,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="387" spans="1:22">
-      <c r="A387" s="14" t="s">
-        <v>220</v>
+    <row r="387" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A387" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B387" s="2">
         <v>0.15790000000000001</v>
@@ -28479,9 +27126,9 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="388" spans="1:22">
-      <c r="A388" s="2" t="s">
-        <v>221</v>
+    <row r="388" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A388" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B388" s="2">
         <v>0.2</v>
@@ -28547,9 +27194,9 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="389" spans="1:22" ht="18" customHeight="1">
-      <c r="A389" s="15" t="s">
-        <v>222</v>
+    <row r="389" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A389" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B389" s="2">
         <v>0.15</v>
@@ -28615,9 +27262,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="390" spans="1:22">
-      <c r="A390" s="2" t="s">
-        <v>223</v>
+    <row r="390" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A390" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B390" s="2">
         <v>0.2</v>
@@ -28683,9 +27330,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="391" spans="1:22">
-      <c r="A391" s="2" t="s">
-        <v>224</v>
+    <row r="391" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A391" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B391" s="2">
         <v>0.18</v>
@@ -28751,9 +27398,9 @@
         <v>16.7</v>
       </c>
     </row>
-    <row r="392" spans="1:22">
-      <c r="A392" s="2" t="s">
-        <v>225</v>
+    <row r="392" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A392" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B392" s="2">
         <v>0.16</v>
@@ -28819,9 +27466,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="393" spans="1:22">
-      <c r="A393" s="2" t="s">
-        <v>226</v>
+    <row r="393" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A393" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B393" s="2">
         <v>9.0899999999999995E-2</v>
@@ -28887,9 +27534,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="394" spans="1:22">
-      <c r="A394" s="2" t="s">
-        <v>227</v>
+    <row r="394" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A394" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B394" s="2">
         <v>6.8199999999999997E-2</v>
@@ -28955,9 +27602,9 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="395" spans="1:22">
-      <c r="A395" s="2" t="s">
-        <v>228</v>
+    <row r="395" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A395" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B395" s="2">
         <v>4.5499999999999999E-2</v>
@@ -29023,9 +27670,9 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="396" spans="1:22">
-      <c r="A396" s="2" t="s">
-        <v>229</v>
+    <row r="396" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A396" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B396" s="2">
         <v>3.0300000000000001E-2</v>
@@ -29091,9 +27738,9 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="397" spans="1:22">
-      <c r="A397" s="2" t="s">
-        <v>230</v>
+    <row r="397" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A397" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B397" s="2">
         <v>0.05</v>
@@ -29159,9 +27806,9 @@
         <v>72.7</v>
       </c>
     </row>
-    <row r="398" spans="1:22">
-      <c r="A398" s="2" t="s">
-        <v>230</v>
+    <row r="398" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A398" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B398" s="2">
         <v>0.05</v>
@@ -29227,9 +27874,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:22">
-      <c r="A399" s="2" t="s">
-        <v>230</v>
+    <row r="399" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A399" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B399" s="2">
         <v>0.05</v>
@@ -29295,9 +27942,9 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="400" spans="1:22">
-      <c r="A400" s="2" t="s">
-        <v>230</v>
+    <row r="400" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A400" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B400" s="2">
         <v>0.05</v>
@@ -29363,9 +28010,9 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="401" spans="1:22">
-      <c r="A401" s="2" t="s">
-        <v>230</v>
+    <row r="401" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A401" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B401" s="2">
         <v>0.05</v>
@@ -29431,9 +28078,9 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="402" spans="1:22">
-      <c r="A402" s="2" t="s">
-        <v>230</v>
+    <row r="402" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A402" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B402" s="2">
         <v>0.05</v>
@@ -29499,9 +28146,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="403" spans="1:22">
-      <c r="A403" s="2" t="s">
-        <v>230</v>
+    <row r="403" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A403" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B403" s="2">
         <v>0.05</v>
@@ -29567,9 +28214,9 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="404" spans="1:22">
-      <c r="A404" s="2" t="s">
-        <v>230</v>
+    <row r="404" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A404" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B404" s="2">
         <v>0.05</v>
@@ -29635,9 +28282,9 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="405" spans="1:22">
-      <c r="A405" s="2" t="s">
-        <v>230</v>
+    <row r="405" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A405" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B405" s="2">
         <v>0.05</v>
@@ -29703,9 +28350,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="406" spans="1:22">
-      <c r="A406" s="2" t="s">
-        <v>230</v>
+    <row r="406" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A406" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B406" s="2">
         <v>0.05</v>
@@ -29771,9 +28418,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:22">
-      <c r="A407" s="2" t="s">
-        <v>230</v>
+    <row r="407" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A407" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B407" s="2">
         <v>0.05</v>
@@ -29839,9 +28486,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="408" spans="1:22">
-      <c r="A408" s="2" t="s">
-        <v>230</v>
+    <row r="408" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A408" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B408" s="2">
         <v>0.05</v>
@@ -29907,9 +28554,9 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="409" spans="1:22">
-      <c r="A409" s="2" t="s">
-        <v>230</v>
+    <row r="409" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A409" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B409" s="2">
         <v>0.05</v>
@@ -29975,9 +28622,9 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="410" spans="1:22">
-      <c r="A410" s="2" t="s">
-        <v>231</v>
+    <row r="410" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A410" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B410" s="2">
         <v>0.17</v>
@@ -30043,9 +28690,9 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="411" spans="1:22">
-      <c r="A411" s="2" t="s">
-        <v>139</v>
+    <row r="411" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A411" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B411" s="2">
         <v>0</v>
@@ -30111,9 +28758,9 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="412" spans="1:22">
-      <c r="A412" s="2" t="s">
-        <v>139</v>
+    <row r="412" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A412" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B412" s="2">
         <v>0</v>
@@ -30179,9 +28826,9 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="413" spans="1:22">
-      <c r="A413" s="2" t="s">
-        <v>112</v>
+    <row r="413" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A413" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B413" s="2">
         <v>0.16389999999999999</v>
@@ -30247,9 +28894,9 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="414" spans="1:22">
-      <c r="A414" s="2" t="s">
-        <v>112</v>
+    <row r="414" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A414" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B414" s="2">
         <v>0.16389999999999999</v>
@@ -30315,9 +28962,9 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="415" spans="1:22">
-      <c r="A415" s="2" t="s">
-        <v>112</v>
+    <row r="415" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A415" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B415" s="2">
         <v>0.16389999999999999</v>
@@ -30383,9 +29030,9 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="416" spans="1:22">
-      <c r="A416" s="2" t="s">
-        <v>112</v>
+    <row r="416" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A416" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B416" s="2">
         <v>0.16389999999999999</v>
@@ -30451,9 +29098,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="417" spans="1:22">
-      <c r="A417" s="2" t="s">
-        <v>112</v>
+    <row r="417" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A417" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B417" s="2">
         <v>0.16389999999999999</v>
@@ -30519,9 +29166,9 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="418" spans="1:22" ht="18">
-      <c r="A418" s="2" t="s">
-        <v>232</v>
+    <row r="418" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A418" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B418" s="2">
         <v>0.125</v>
@@ -30587,9 +29234,9 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="419" spans="1:22" ht="18">
-      <c r="A419" s="2" t="s">
-        <v>233</v>
+    <row r="419" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A419" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B419" s="2">
         <v>6.25E-2</v>
@@ -30655,9 +29302,9 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="420" spans="1:22">
-      <c r="A420" s="2" t="s">
-        <v>234</v>
+    <row r="420" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A420" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B420" s="2">
         <v>0</v>
@@ -30723,9 +29370,9 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="421" spans="1:22" ht="16">
-      <c r="A421" s="2" t="s">
-        <v>139</v>
+    <row r="421" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A421" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B421" s="2">
         <v>0</v>
@@ -30791,9 +29438,9 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="422" spans="1:22" ht="16">
-      <c r="A422" s="2" t="s">
-        <v>139</v>
+    <row r="422" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A422" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B422" s="2">
         <v>0</v>
@@ -30859,9 +29506,9 @@
         <v>33.9</v>
       </c>
     </row>
-    <row r="423" spans="1:22" ht="16">
-      <c r="A423" s="2" t="s">
-        <v>139</v>
+    <row r="423" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A423" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B423" s="2">
         <v>0</v>
@@ -30927,9 +29574,9 @@
         <v>44.1</v>
       </c>
     </row>
-    <row r="424" spans="1:22" ht="16">
-      <c r="A424" s="2" t="s">
-        <v>139</v>
+    <row r="424" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A424" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B424" s="2">
         <v>0</v>
@@ -30995,9 +29642,9 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="425" spans="1:22">
-      <c r="A425" s="2" t="s">
-        <v>235</v>
+    <row r="425" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A425" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B425" s="2">
         <v>0.1613</v>
@@ -31063,9 +29710,9 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="426" spans="1:22">
-      <c r="A426" s="2" t="s">
-        <v>236</v>
+    <row r="426" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A426" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B426" s="2">
         <v>0.15870000000000001</v>
@@ -31131,9 +29778,9 @@
         <v>24.6</v>
       </c>
     </row>
-    <row r="427" spans="1:22">
-      <c r="A427" s="2" t="s">
-        <v>237</v>
+    <row r="427" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A427" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B427" s="2">
         <v>0.15629999999999999</v>
@@ -31199,9 +29846,9 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:22" ht="16">
-      <c r="A428" s="2" t="s">
-        <v>139</v>
+    <row r="428" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A428" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B428" s="2">
         <v>0</v>
@@ -31267,9 +29914,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="429" spans="1:22" ht="16">
-      <c r="A429" s="2" t="s">
-        <v>139</v>
+    <row r="429" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A429" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B429" s="2">
         <v>0</v>
@@ -31335,9 +29982,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="430" spans="1:22" ht="16">
-      <c r="A430" s="2" t="s">
-        <v>139</v>
+    <row r="430" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A430" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B430" s="2">
         <v>0</v>
@@ -31403,9 +30050,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="431" spans="1:22" ht="16">
-      <c r="A431" s="2" t="s">
-        <v>139</v>
+    <row r="431" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A431" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B431" s="2">
         <v>0</v>
@@ -31471,9 +30118,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="432" spans="1:22" ht="16">
-      <c r="A432" s="2" t="s">
-        <v>139</v>
+    <row r="432" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A432" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B432" s="2">
         <v>0</v>
@@ -31539,9 +30186,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="433" spans="1:22">
-      <c r="A433" s="2" t="s">
-        <v>238</v>
+    <row r="433" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A433" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B433" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31607,9 +30254,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="434" spans="1:22">
-      <c r="A434" s="2" t="s">
-        <v>238</v>
+    <row r="434" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A434" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B434" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31675,9 +30322,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="435" spans="1:22">
-      <c r="A435" s="2" t="s">
-        <v>238</v>
+    <row r="435" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A435" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B435" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31743,9 +30390,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="436" spans="1:22">
-      <c r="A436" s="2" t="s">
-        <v>238</v>
+    <row r="436" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A436" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B436" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31811,9 +30458,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="437" spans="1:22">
-      <c r="A437" s="2" t="s">
-        <v>238</v>
+    <row r="437" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A437" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B437" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31879,9 +30526,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="438" spans="1:22">
-      <c r="A438" s="2" t="s">
-        <v>238</v>
+    <row r="438" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A438" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B438" s="2">
         <v>6.9800000000000001E-2</v>
@@ -31947,9 +30594,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439" spans="1:22">
-      <c r="A439" s="2" t="s">
-        <v>238</v>
+    <row r="439" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A439" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B439" s="2">
         <v>6.9800000000000001E-2</v>
@@ -32015,9 +30662,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="440" spans="1:22">
-      <c r="A440" s="2" t="s">
-        <v>238</v>
+    <row r="440" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A440" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B440" s="2">
         <v>6.9800000000000001E-2</v>
@@ -32083,9 +30730,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="441" spans="1:22">
-      <c r="A441" s="2" t="s">
-        <v>238</v>
+    <row r="441" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A441" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B441" s="2">
         <v>6.9800000000000001E-2</v>
@@ -32151,9 +30798,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="442" spans="1:22">
-      <c r="A442" s="2" t="s">
-        <v>239</v>
+    <row r="442" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A442" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B442" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32219,9 +30866,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="443" spans="1:22">
-      <c r="A443" s="2" t="s">
-        <v>239</v>
+    <row r="443" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A443" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B443" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32287,9 +30934,9 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="444" spans="1:22">
-      <c r="A444" s="2" t="s">
-        <v>239</v>
+    <row r="444" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A444" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B444" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32355,9 +31002,9 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="445" spans="1:22">
-      <c r="A445" s="2" t="s">
-        <v>239</v>
+    <row r="445" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A445" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B445" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32423,9 +31070,9 @@
         <v>38.700000000000003</v>
       </c>
     </row>
-    <row r="446" spans="1:22">
-      <c r="A446" s="2" t="s">
-        <v>239</v>
+    <row r="446" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A446" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B446" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32491,9 +31138,9 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="447" spans="1:22">
-      <c r="A447" s="2" t="s">
-        <v>239</v>
+    <row r="447" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A447" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B447" s="2">
         <v>2.4400000000000002E-2</v>
@@ -32559,9 +31206,9 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="448" spans="1:22">
-      <c r="A448" s="2" t="s">
-        <v>240</v>
+    <row r="448" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A448" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B448" s="2">
         <v>0.2</v>
@@ -32627,9 +31274,9 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="449" spans="1:22">
-      <c r="A449" s="2" t="s">
-        <v>241</v>
+    <row r="449" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A449" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B449" s="2">
         <v>0.25</v>
@@ -32695,9 +31342,9 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="450" spans="1:22">
-      <c r="A450" s="2" t="s">
-        <v>242</v>
+    <row r="450" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A450" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B450" s="2">
         <v>0.3</v>
@@ -32763,9 +31410,9 @@
         <v>41.53</v>
       </c>
     </row>
-    <row r="451" spans="1:22">
-      <c r="A451" s="2" t="s">
-        <v>243</v>
+    <row r="451" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A451" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B451" s="2">
         <v>9.5000000000000001E-2</v>
@@ -32831,9 +31478,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="452" spans="1:22" ht="16">
-      <c r="A452" s="2" t="s">
-        <v>244</v>
+    <row r="452" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A452" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B452" s="2">
         <v>0.19</v>
@@ -32899,9 +31546,9 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="453" spans="1:22" ht="16">
-      <c r="A453" s="2" t="s">
-        <v>245</v>
+    <row r="453" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A453" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B453" s="8">
         <v>0.2</v>
@@ -32967,9 +31614,9 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="454" spans="1:22" ht="16">
-      <c r="A454" s="2" t="s">
-        <v>246</v>
+    <row r="454" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A454" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B454" s="2">
         <v>0.21</v>
@@ -33035,9 +31682,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="455" spans="1:22" ht="16">
-      <c r="A455" s="2" t="s">
-        <v>123</v>
+    <row r="455" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A455" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B455" s="2">
         <v>0.1724</v>
@@ -33103,9 +31750,9 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="456" spans="1:22" ht="16">
-      <c r="A456" s="2" t="s">
-        <v>123</v>
+    <row r="456" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A456" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B456" s="2">
         <v>0.1724</v>
@@ -33171,9 +31818,9 @@
         <v>14.22</v>
       </c>
     </row>
-    <row r="457" spans="1:22">
-      <c r="A457" s="2" t="s">
-        <v>87</v>
+    <row r="457" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A457" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B457" s="2">
         <v>0.25</v>
@@ -33239,9 +31886,9 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="458" spans="1:22">
-      <c r="A458" s="2" t="s">
-        <v>87</v>
+    <row r="458" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A458" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B458" s="2">
         <v>0.25</v>
@@ -33307,9 +31954,9 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="459" spans="1:22">
-      <c r="A459" s="2" t="s">
-        <v>247</v>
+    <row r="459" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A459" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B459" s="2">
         <v>0.19400000000000001</v>
@@ -33375,9 +32022,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="460" spans="1:22" ht="16">
-      <c r="A460" s="2" t="s">
-        <v>247</v>
+    <row r="460" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A460" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B460" s="2">
         <v>0.19400000000000001</v>
@@ -33443,9 +32090,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="461" spans="1:22">
-      <c r="A461" s="2" t="s">
-        <v>22</v>
+    <row r="461" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A461" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B461" s="2">
         <v>0.16389999999999999</v>
@@ -33511,9 +32158,9 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="462" spans="1:22" ht="18">
-      <c r="A462" s="2" t="s">
-        <v>202</v>
+    <row r="462" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A462" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B462" s="2">
         <v>4.7600000000000003E-2</v>
@@ -33579,9 +32226,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="463" spans="1:22">
-      <c r="A463" s="2" t="s">
-        <v>248</v>
+    <row r="463" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A463" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B463" s="2">
         <v>0.17</v>
@@ -33647,9 +32294,9 @@
         <v>19.09</v>
       </c>
     </row>
-    <row r="464" spans="1:22" ht="21" customHeight="1">
-      <c r="A464" s="2" t="s">
-        <v>249</v>
+    <row r="464" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A464" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B464" s="2">
         <v>0</v>
@@ -33715,9 +32362,9 @@
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="465" spans="1:22" ht="21" customHeight="1">
-      <c r="A465" s="2" t="s">
-        <v>250</v>
+    <row r="465" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A465" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B465" s="2">
         <v>7.4099999999999999E-2</v>
@@ -33783,9 +32430,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="466" spans="1:22" ht="21" customHeight="1">
-      <c r="A466" s="2" t="s">
-        <v>251</v>
+    <row r="466" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A466" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B466" s="2">
         <v>0.1071</v>
@@ -33851,9 +32498,9 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="467" spans="1:22" ht="21" customHeight="1">
-      <c r="A467" s="2" t="s">
-        <v>252</v>
+    <row r="467" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A467" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B467" s="2">
         <v>0.13789999999999999</v>
@@ -33919,9 +32566,9 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="468" spans="1:22">
-      <c r="A468" s="2" t="s">
-        <v>86</v>
+    <row r="468" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A468" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B468" s="2">
         <v>0.1111</v>
@@ -33987,9 +32634,9 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="469" spans="1:22">
-      <c r="A469" s="2" t="s">
-        <v>181</v>
+    <row r="469" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A469" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B469" s="2">
         <v>0.13039999999999999</v>
@@ -34055,9 +32702,9 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="470" spans="1:22">
-      <c r="A470" s="2" t="s">
-        <v>181</v>
+    <row r="470" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A470" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B470" s="2">
         <v>0.13039999999999999</v>
@@ -34123,9 +32770,9 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="471" spans="1:22">
-      <c r="A471" s="2" t="s">
-        <v>180</v>
+    <row r="471" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A471" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B471" s="2">
         <v>0.1489</v>
@@ -34191,9 +32838,9 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="472" spans="1:22">
-      <c r="A472" s="2" t="s">
-        <v>180</v>
+    <row r="472" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A472" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B472" s="2">
         <v>0.1489</v>
@@ -34259,9 +32906,9 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="473" spans="1:22">
-      <c r="A473" s="2" t="s">
-        <v>253</v>
+    <row r="473" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A473" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B473" s="2">
         <v>0.16669999999999999</v>
@@ -34327,9 +32974,9 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="474" spans="1:22">
-      <c r="A474" s="2" t="s">
-        <v>254</v>
+    <row r="474" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A474" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B474" s="2">
         <v>2.4400000000000002E-2</v>
@@ -34395,9 +33042,9 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="475" spans="1:22">
-      <c r="A475" s="2" t="s">
-        <v>22</v>
+    <row r="475" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A475" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B475" s="2">
         <v>0.16389999999999999</v>
@@ -34463,9 +33110,9 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="476" spans="1:22">
-      <c r="A476" s="2" t="s">
-        <v>22</v>
+    <row r="476" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A476" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B476" s="2">
         <v>0.16389999999999999</v>
@@ -34531,9 +33178,9 @@
         <v>24.9</v>
       </c>
     </row>
-    <row r="477" spans="1:22">
-      <c r="A477" s="2" t="s">
-        <v>139</v>
+    <row r="477" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A477" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B477" s="2">
         <v>0</v>
@@ -34599,9 +33246,9 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="478" spans="1:22">
-      <c r="A478" s="2" t="s">
-        <v>139</v>
+    <row r="478" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A478" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B478" s="2">
         <v>0</v>
@@ -34667,9 +33314,9 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="479" spans="1:22">
-      <c r="A479" s="2" t="s">
-        <v>139</v>
+    <row r="479" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A479" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B479" s="2">
         <v>0</v>
@@ -34735,9 +33382,9 @@
         <v>9.6300000000000008</v>
       </c>
     </row>
-    <row r="480" spans="1:22">
-      <c r="A480" s="2" t="s">
-        <v>139</v>
+    <row r="480" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A480" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B480" s="2">
         <v>0</v>
@@ -34803,9 +33450,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:22">
-      <c r="A481" s="2" t="s">
-        <v>22</v>
+    <row r="481" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A481" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B481" s="2">
         <v>0.16389999999999999</v>
@@ -34871,9 +33518,9 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="482" spans="1:22">
-      <c r="A482" s="2" t="s">
-        <v>22</v>
+    <row r="482" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A482" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B482" s="2">
         <v>0.16389999999999999</v>
@@ -34939,9 +33586,9 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="483" spans="1:22">
-      <c r="A483" s="2" t="s">
-        <v>22</v>
+    <row r="483" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A483" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B483" s="2">
         <v>0.16389999999999999</v>
@@ -35007,9 +33654,9 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="484" spans="1:22">
-      <c r="A484" s="2" t="s">
-        <v>22</v>
+    <row r="484" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A484" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B484" s="2">
         <v>0.16389999999999999</v>
@@ -35075,9 +33722,9 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="485" spans="1:22" ht="16">
-      <c r="A485" s="2" t="s">
-        <v>139</v>
+    <row r="485" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A485" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B485" s="2">
         <v>0</v>
@@ -35143,9 +33790,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="486" spans="1:22" ht="16">
-      <c r="A486" s="2" t="s">
-        <v>139</v>
+    <row r="486" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A486" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B486" s="2">
         <v>0</v>
@@ -35211,9 +33858,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:22" ht="16">
-      <c r="A487" s="2" t="s">
-        <v>139</v>
+    <row r="487" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A487" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B487" s="2">
         <v>0</v>
@@ -35279,9 +33926,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="488" spans="1:22" ht="16">
-      <c r="A488" s="2" t="s">
-        <v>139</v>
+    <row r="488" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A488" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B488" s="2">
         <v>0</v>
@@ -35347,9 +33994,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="489" spans="1:22" ht="16">
-      <c r="A489" s="2" t="s">
-        <v>139</v>
+    <row r="489" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A489" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B489" s="2">
         <v>0</v>
@@ -35415,9 +34062,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:22">
-      <c r="A490" s="2" t="s">
-        <v>181</v>
+    <row r="490" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A490" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B490" s="2">
         <v>0.13039999999999999</v>
@@ -35483,9 +34130,9 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="491" spans="1:22">
-      <c r="A491" s="2" t="s">
-        <v>181</v>
+    <row r="491" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A491" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B491" s="2">
         <v>0.13039999999999999</v>
@@ -35551,9 +34198,9 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="492" spans="1:22">
-      <c r="A492" s="2" t="s">
-        <v>255</v>
+    <row r="492" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A492" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B492" s="2">
         <v>0.15379999999999999</v>
@@ -35619,9 +34266,9 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="493" spans="1:22">
-      <c r="A493" s="2" t="s">
-        <v>255</v>
+    <row r="493" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A493" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B493" s="2">
         <v>0.15379999999999999</v>
@@ -35687,9 +34334,9 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="494" spans="1:22">
-      <c r="A494" s="2" t="s">
-        <v>255</v>
+    <row r="494" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A494" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B494" s="2">
         <v>0.15379999999999999</v>
@@ -35755,9 +34402,9 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="495" spans="1:22">
-      <c r="A495" s="2" t="s">
-        <v>256</v>
+    <row r="495" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A495" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B495" s="2">
         <v>4.7600000000000003E-2</v>
@@ -35823,9 +34470,9 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="496" spans="1:22">
-      <c r="A496" s="2" t="s">
-        <v>257</v>
+    <row r="496" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A496" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B496" s="2">
         <v>0.1111</v>
@@ -35891,9 +34538,9 @@
         <v>32.200000000000003</v>
       </c>
     </row>
-    <row r="497" spans="1:22">
-      <c r="A497" s="2" t="s">
-        <v>258</v>
+    <row r="497" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A497" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B497" s="2">
         <v>0.2</v>
@@ -35959,9 +34606,9 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="498" spans="1:22" ht="16">
-      <c r="A498" s="2" t="s">
-        <v>22</v>
+    <row r="498" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A498" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B498" s="2">
         <v>0.16389999999999999</v>
@@ -36027,9 +34674,9 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="499" spans="1:22" ht="16">
-      <c r="A499" s="2" t="s">
-        <v>259</v>
+    <row r="499" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A499" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B499" s="2">
         <v>0.1613</v>
@@ -36095,9 +34742,9 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="500" spans="1:22" ht="16">
-      <c r="A500" s="2" t="s">
-        <v>260</v>
+    <row r="500" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A500" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B500" s="2">
         <v>0.14710000000000001</v>
@@ -36163,9 +34810,9 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="501" spans="1:22">
-      <c r="A501" s="2" t="s">
-        <v>261</v>
+    <row r="501" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A501" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B501" s="2">
         <v>0</v>
@@ -36231,9 +34878,9 @@
         <v>96.2</v>
       </c>
     </row>
-    <row r="502" spans="1:22">
-      <c r="A502" s="2" t="s">
-        <v>262</v>
+    <row r="502" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A502" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B502" s="2">
         <v>0.1905</v>
@@ -36299,9 +34946,9 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="503" spans="1:22">
-      <c r="A503" s="2" t="s">
-        <v>262</v>
+    <row r="503" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A503" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B503" s="2">
         <v>0.1905</v>
@@ -36367,9 +35014,9 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="504" spans="1:22">
-      <c r="A504" s="2" t="s">
-        <v>262</v>
+    <row r="504" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A504" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B504" s="2">
         <v>0.1905</v>
@@ -36435,9 +35082,9 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="505" spans="1:22" ht="15">
-      <c r="A505" s="3" t="s">
-        <v>263</v>
+    <row r="505" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A505" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B505" s="2">
         <v>0.1961</v>
@@ -36503,9 +35150,9 @@
         <v>37.9</v>
       </c>
     </row>
-    <row r="506" spans="1:22">
-      <c r="A506" s="2" t="s">
-        <v>264</v>
+    <row r="506" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A506" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B506" s="2">
         <v>0.18690000000000001</v>
@@ -36571,9 +35218,9 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="507" spans="1:22">
-      <c r="A507" s="2" t="s">
-        <v>265</v>
+    <row r="507" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A507" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B507" s="2">
         <v>0.17860000000000001</v>
@@ -36639,9 +35286,9 @@
         <v>47.6</v>
       </c>
     </row>
-    <row r="508" spans="1:22">
-      <c r="A508" s="2" t="s">
-        <v>266</v>
+    <row r="508" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A508" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B508" s="2">
         <v>0.1709</v>
@@ -36707,9 +35354,9 @@
         <v>46.9</v>
       </c>
     </row>
-    <row r="509" spans="1:22">
-      <c r="A509" s="2" t="s">
-        <v>22</v>
+    <row r="509" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A509" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B509" s="2">
         <v>0.16389999999999999</v>
@@ -36775,9 +35422,9 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="510" spans="1:22">
-      <c r="A510" s="2" t="s">
-        <v>265</v>
+    <row r="510" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A510" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B510" s="2">
         <v>0.17860000000000001</v>
@@ -36843,9 +35490,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="511" spans="1:22">
-      <c r="A511" s="2" t="s">
-        <v>265</v>
+    <row r="511" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A511" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B511" s="2">
         <v>0.17860000000000001</v>
@@ -36911,9 +35558,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="512" spans="1:22">
-      <c r="A512" s="2" t="s">
-        <v>265</v>
+    <row r="512" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A512" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B512" s="2">
         <v>0.17860000000000001</v>
@@ -36979,9 +35626,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="513" spans="1:22">
-      <c r="A513" s="2" t="s">
-        <v>267</v>
+    <row r="513" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A513" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B513" s="2">
         <v>0.17860000000000001</v>
@@ -37047,9 +35694,9 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="514" spans="1:22">
-      <c r="A514" s="2" t="s">
-        <v>268</v>
+    <row r="514" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A514" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B514" s="2">
         <v>0</v>
@@ -37115,9 +35762,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="515" spans="1:22">
-      <c r="A515" s="2" t="s">
-        <v>269</v>
+    <row r="515" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A515" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B515" s="2">
         <v>0</v>
@@ -37183,9 +35830,9 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="516" spans="1:22">
-      <c r="A516" s="2" t="s">
-        <v>270</v>
+    <row r="516" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A516" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B516" s="2">
         <v>0</v>
@@ -37251,9 +35898,9 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="517" spans="1:22">
-      <c r="A517" s="2" t="s">
-        <v>271</v>
+    <row r="517" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A517" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B517" s="2">
         <v>0</v>
@@ -37319,9 +35966,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="518" spans="1:22">
-      <c r="A518" s="2" t="s">
-        <v>272</v>
+    <row r="518" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A518" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B518" s="2">
         <v>0</v>
@@ -37387,9 +36034,9 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="519" spans="1:22">
-      <c r="A519" s="2" t="s">
-        <v>273</v>
+    <row r="519" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A519" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B519" s="2">
         <v>0</v>
@@ -37455,9 +36102,9 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="520" spans="1:22">
-      <c r="A520" s="2" t="s">
-        <v>274</v>
+    <row r="520" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A520" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B520" s="2">
         <v>6.9800000000000001E-2</v>
@@ -37523,9 +36170,9 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="521" spans="1:22" ht="16">
-      <c r="A521" s="2" t="s">
-        <v>22</v>
+    <row r="521" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A521" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B521" s="2">
         <v>0.16389999999999999</v>
@@ -37591,9 +36238,9 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="522" spans="1:22">
-      <c r="A522" s="2" t="s">
-        <v>275</v>
+    <row r="522" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A522" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B522" s="2">
         <v>0.1111</v>
@@ -37659,9 +36306,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="523" spans="1:22">
-      <c r="A523" s="2" t="s">
-        <v>275</v>
+    <row r="523" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A523" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B523" s="2">
         <v>0.1111</v>
@@ -37727,9 +36374,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="524" spans="1:22">
-      <c r="A524" s="2" t="s">
-        <v>275</v>
+    <row r="524" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A524" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B524" s="2">
         <v>0.1111</v>
@@ -37795,9 +36442,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="525" spans="1:22">
-      <c r="A525" s="2" t="s">
-        <v>275</v>
+    <row r="525" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A525" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B525" s="2">
         <v>0.1111</v>
@@ -37863,9 +36510,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="526" spans="1:22">
-      <c r="A526" s="2" t="s">
-        <v>181</v>
+    <row r="526" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A526" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B526" s="2">
         <v>0.13039999999999999</v>
@@ -37931,9 +36578,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="527" spans="1:22">
-      <c r="A527" s="2" t="s">
-        <v>181</v>
+    <row r="527" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A527" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B527" s="2">
         <v>0.13039999999999999</v>
@@ -37999,9 +36646,9 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="528" spans="1:22">
-      <c r="A528" s="2" t="s">
-        <v>181</v>
+    <row r="528" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A528" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B528" s="2">
         <v>0.13039999999999999</v>
@@ -38067,9 +36714,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="529" spans="1:22">
-      <c r="A529" s="2" t="s">
-        <v>181</v>
+    <row r="529" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A529" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B529" s="2">
         <v>0.13039999999999999</v>
@@ -38135,9 +36782,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="530" spans="1:22">
-      <c r="A530" s="2" t="s">
-        <v>181</v>
+    <row r="530" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A530" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B530" s="2">
         <v>0.13039999999999999</v>
@@ -38203,9 +36850,9 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="531" spans="1:22">
-      <c r="A531" s="2" t="s">
-        <v>276</v>
+    <row r="531" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A531" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B531" s="2">
         <v>0.05</v>
@@ -38271,9 +36918,9 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="532" spans="1:22">
-      <c r="A532" s="2" t="s">
-        <v>277</v>
+    <row r="532" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A532" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B532" s="2">
         <v>8.3299999999999999E-2</v>
@@ -38339,9 +36986,9 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="533" spans="1:22">
-      <c r="A533" s="2" t="s">
-        <v>278</v>
+    <row r="533" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A533" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B533" s="2">
         <v>0.1071</v>
@@ -38407,9 +37054,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="534" spans="1:22">
-      <c r="A534" s="2" t="s">
-        <v>279</v>
+    <row r="534" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A534" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B534" s="2">
         <v>0.125</v>
@@ -38475,9 +37122,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="535" spans="1:22">
-      <c r="A535" s="2" t="s">
-        <v>139</v>
+    <row r="535" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A535" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B535" s="2">
         <v>0</v>
@@ -38543,9 +37190,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="536" spans="1:22" ht="18">
-      <c r="A536" s="2" t="s">
-        <v>22</v>
+    <row r="536" spans="1:22" ht="18" x14ac:dyDescent="0.2">
+      <c r="A536" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B536" s="2">
         <v>0.16389999999999999</v>
@@ -38611,9 +37258,9 @@
         <v>25.9</v>
       </c>
     </row>
-    <row r="537" spans="1:22">
-      <c r="A537" s="2" t="s">
-        <v>280</v>
+    <row r="537" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A537" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B537" s="2">
         <v>0</v>
@@ -38679,9 +37326,9 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="538" spans="1:22">
-      <c r="A538" s="2" t="s">
-        <v>281</v>
+    <row r="538" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A538" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B538" s="2">
         <v>0</v>
@@ -38747,9 +37394,9 @@
         <v>69</v>
       </c>
     </row>
-    <row r="539" spans="1:22">
-      <c r="A539" s="2" t="s">
-        <v>282</v>
+    <row r="539" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A539" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B539" s="2">
         <v>0</v>
@@ -38815,9 +37462,9 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="540" spans="1:22">
-      <c r="A540" s="19" t="s">
-        <v>283</v>
+    <row r="540" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A540" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B540" s="2">
         <v>0</v>
@@ -38883,9 +37530,9 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="541" spans="1:22">
-      <c r="A541" s="19" t="s">
-        <v>284</v>
+    <row r="541" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A541" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B541" s="2">
         <v>0</v>
@@ -38951,9 +37598,9 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="542" spans="1:22">
-      <c r="A542" s="19" t="s">
-        <v>285</v>
+    <row r="542" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A542" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B542" s="2">
         <v>0</v>
@@ -39019,9 +37666,9 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="543" spans="1:22">
-      <c r="A543" s="19" t="s">
-        <v>286</v>
+    <row r="543" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A543" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B543" s="2">
         <v>0</v>
@@ -39087,9 +37734,9 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="544" spans="1:22">
-      <c r="A544" s="23" t="s">
-        <v>287</v>
+    <row r="544" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A544" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B544" s="2">
         <v>0</v>
@@ -39155,9 +37802,9 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="545" spans="1:22">
-      <c r="A545" s="2" t="s">
-        <v>288</v>
+    <row r="545" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A545" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B545" s="2">
         <v>0</v>
@@ -39223,9 +37870,9 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="546" spans="1:22">
-      <c r="A546" s="2" t="s">
-        <v>289</v>
+    <row r="546" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A546" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B546" s="2">
         <v>0</v>
@@ -39291,9 +37938,9 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="547" spans="1:22">
-      <c r="A547" s="2" t="s">
-        <v>290</v>
+    <row r="547" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A547" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B547" s="2">
         <v>0</v>
@@ -39359,9 +38006,9 @@
         <v>24.57</v>
       </c>
     </row>
-    <row r="548" spans="1:22">
-      <c r="A548" s="2" t="s">
-        <v>291</v>
+    <row r="548" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A548" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B548" s="2">
         <v>0</v>
@@ -39427,9 +38074,9 @@
         <v>13.46</v>
       </c>
     </row>
-    <row r="549" spans="1:22">
-      <c r="A549" s="2" t="s">
-        <v>292</v>
+    <row r="549" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A549" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B549" s="2">
         <v>0</v>
@@ -39495,9 +38142,9 @@
         <v>6.83</v>
       </c>
     </row>
-    <row r="550" spans="1:22">
-      <c r="A550" s="2" t="s">
-        <v>293</v>
+    <row r="550" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A550" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B550" s="2">
         <v>0.18179999999999999</v>
@@ -39563,9 +38210,9 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="551" spans="1:22">
-      <c r="A551" s="2" t="s">
-        <v>294</v>
+    <row r="551" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A551" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B551" s="2">
         <v>0.1429</v>
@@ -39631,9 +38278,9 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="552" spans="1:22">
-      <c r="A552" s="2" t="s">
-        <v>295</v>
+    <row r="552" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A552" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B552" s="2">
         <v>0.125</v>
@@ -39699,9 +38346,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="553" spans="1:22">
-      <c r="A553" s="2" t="s">
-        <v>296</v>
+    <row r="553" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A553" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B553" s="2">
         <v>0.17</v>
@@ -39767,9 +38414,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:22" ht="16">
-      <c r="A554" s="2" t="s">
-        <v>296</v>
+    <row r="554" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A554" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B554" s="2">
         <v>0.17</v>
@@ -39835,9 +38482,9 @@
         <v>22.04</v>
       </c>
     </row>
-    <row r="555" spans="1:22" ht="16">
-      <c r="A555" s="2" t="s">
-        <v>296</v>
+    <row r="555" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A555" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B555" s="2">
         <v>0.17</v>
@@ -39903,9 +38550,9 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="556" spans="1:22" ht="16">
-      <c r="A556" s="2" t="s">
-        <v>296</v>
+    <row r="556" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A556" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B556" s="2">
         <v>0.17</v>
@@ -39971,9 +38618,9 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="557" spans="1:22" ht="16">
-      <c r="A557" s="2" t="s">
-        <v>297</v>
+    <row r="557" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A557" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B557" s="2">
         <v>0.16</v>
@@ -40039,9 +38686,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="558" spans="1:22" ht="16">
-      <c r="A558" s="5" t="s">
-        <v>298</v>
+    <row r="558" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A558" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B558" s="2">
         <v>0.17860000000000001</v>
@@ -40107,9 +38754,9 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="559" spans="1:22" ht="16">
-      <c r="A559" s="5" t="s">
-        <v>299</v>
+    <row r="559" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A559" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B559" s="2">
         <v>0.17699999999999999</v>
@@ -40175,9 +38822,9 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="560" spans="1:22" ht="16">
-      <c r="A560" s="5" t="s">
-        <v>300</v>
+    <row r="560" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A560" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B560" s="2">
         <v>0.1754</v>
@@ -40243,9 +38890,9 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="561" spans="1:22" ht="16">
-      <c r="A561" s="5" t="s">
-        <v>301</v>
+    <row r="561" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A561" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B561" s="2">
         <v>0.1739</v>
@@ -40311,9 +38958,9 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="562" spans="1:22" ht="16">
-      <c r="A562" s="5" t="s">
-        <v>302</v>
+    <row r="562" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A562" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B562" s="2">
         <v>0.1724</v>
@@ -40379,9 +39026,9 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="563" spans="1:22" ht="16">
-      <c r="A563" s="5" t="s">
-        <v>303</v>
+    <row r="563" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A563" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B563" s="2">
         <v>0.16950000000000001</v>
@@ -40447,9 +39094,9 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="564" spans="1:22" ht="16">
-      <c r="A564" s="5" t="s">
-        <v>304</v>
+    <row r="564" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A564" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B564" s="2">
         <v>0.16669999999999999</v>
@@ -40515,9 +39162,9 @@
         <v>17.170000000000002</v>
       </c>
     </row>
-    <row r="565" spans="1:22" ht="16">
-      <c r="A565" s="5" t="s">
-        <v>305</v>
+    <row r="565" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A565" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B565" s="2">
         <v>0.16389999999999999</v>
@@ -40583,9 +39230,9 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="566" spans="1:22" ht="16">
-      <c r="A566" s="5" t="s">
-        <v>306</v>
+    <row r="566" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A566" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B566" s="2">
         <v>0.15379999999999999</v>
@@ -40651,9 +39298,9 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="567" spans="1:22" ht="16">
-      <c r="A567" s="5" t="s">
-        <v>307</v>
+    <row r="567" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A567" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B567" s="2">
         <v>0.1754</v>
@@ -40719,9 +39366,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="568" spans="1:22" ht="16">
-      <c r="A568" s="5" t="s">
-        <v>308</v>
+    <row r="568" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A568" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B568" s="2">
         <v>0.1754</v>
@@ -40787,9 +39434,9 @@
         <v>17.329999999999998</v>
       </c>
     </row>
-    <row r="569" spans="1:22" ht="16">
-      <c r="A569" s="5" t="s">
-        <v>309</v>
+    <row r="569" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A569" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B569" s="2">
         <v>0.1724</v>
@@ -40855,9 +39502,9 @@
         <v>15.11</v>
       </c>
     </row>
-    <row r="570" spans="1:22" ht="16">
-      <c r="A570" s="5" t="s">
-        <v>310</v>
+    <row r="570" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A570" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B570" s="2">
         <v>0.1724</v>
@@ -40923,9 +39570,9 @@
         <v>8.08</v>
       </c>
     </row>
-    <row r="571" spans="1:22" ht="16">
-      <c r="A571" s="5" t="s">
-        <v>311</v>
+    <row r="571" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A571" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B571" s="2">
         <v>0.1724</v>
@@ -40991,9 +39638,9 @@
         <v>18.809999999999999</v>
       </c>
     </row>
-    <row r="572" spans="1:22" ht="16">
-      <c r="A572" s="5" t="s">
-        <v>312</v>
+    <row r="572" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A572" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B572" s="2">
         <v>0.16389999999999999</v>
@@ -41059,9 +39706,9 @@
         <v>10.220000000000001</v>
       </c>
     </row>
-    <row r="573" spans="1:22" ht="16">
-      <c r="A573" s="5" t="s">
-        <v>313</v>
+    <row r="573" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A573" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B573" s="2">
         <v>0.16389999999999999</v>
@@ -41127,9 +39774,9 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="574" spans="1:22" ht="16">
-      <c r="A574" s="5" t="s">
-        <v>314</v>
+    <row r="574" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A574" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B574" s="2">
         <v>0.16389999999999999</v>
@@ -41195,9 +39842,9 @@
         <v>13.98</v>
       </c>
     </row>
-    <row r="575" spans="1:22" ht="16">
-      <c r="A575" s="5" t="s">
-        <v>315</v>
+    <row r="575" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A575" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B575" s="2">
         <v>0.15379999999999999</v>
@@ -41263,9 +39910,9 @@
         <v>21.46</v>
       </c>
     </row>
-    <row r="576" spans="1:22" ht="16">
-      <c r="A576" s="5" t="s">
-        <v>316</v>
+    <row r="576" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A576" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B576" s="2">
         <v>0.15379999999999999</v>
@@ -41331,9 +39978,9 @@
         <v>26.12</v>
       </c>
     </row>
-    <row r="577" spans="1:22" ht="16">
-      <c r="A577" s="5" t="s">
-        <v>317</v>
+    <row r="577" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A577" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B577" s="2">
         <v>0.15379999999999999</v>
@@ -41399,9 +40046,9 @@
         <v>28.05</v>
       </c>
     </row>
-    <row r="578" spans="1:22" ht="16">
-      <c r="A578" s="5" t="s">
-        <v>318</v>
+    <row r="578" spans="1:22" ht="16" x14ac:dyDescent="0.2">
+      <c r="A578" s="25" t="s">
+        <v>23</v>
       </c>
       <c r="B578" s="2">
         <v>0.15379999999999999</v>
